--- a/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1608A1-C742-4B29-81AC-F4C1ECB8341B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8BA023-242B-48B0-B325-4E669396DC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="215">
   <si>
     <t>Key</t>
   </si>
@@ -331,27 +331,12 @@
     <t>Volumes do Caderno SUS</t>
   </si>
   <si>
-    <t>"Atendimento Ambulatorial e Atendimento Imediato"</t>
-  </si>
-  <si>
-    <t>"Internação e Apoio ao Diagnóstico e à Terapia (Reabilitação)"</t>
-  </si>
-  <si>
-    <t>"Apoio ao Diagnóstico e à Terapia (Imagenologia)"</t>
-  </si>
-  <si>
-    <t>"Apoio ao Diagnóstico e à Terapia (Anatomia Patológica, Patologia Clínica, Hemoterapia e Hematologia, Medicina Nuclear)"</t>
-  </si>
-  <si>
     <t>tema</t>
   </si>
   <si>
     <t>descrição</t>
   </si>
   <si>
-    <t>"Volume do caderno do SomaSUS"</t>
-  </si>
-  <si>
     <t>Interop</t>
   </si>
   <si>
@@ -719,6 +704,27 @@
   </si>
   <si>
     <t>Hospitalar</t>
+  </si>
+  <si>
+    <t>"[ 5I.10.28 ]"</t>
+  </si>
+  <si>
+    <t>código.abnt</t>
+  </si>
+  <si>
+    <t>"Caderno do SomaSUS"</t>
+  </si>
+  <si>
+    <t>"Volume 1 - Atendimento Ambulatorial e Atendimento Imediato"</t>
+  </si>
+  <si>
+    <t>"Volume 4 - Apoio ao Diagnóstico e à Terapia (Anatomia Patológica, Patologia Clínica, Hemoterapia e Hematologia, Medicina Nuclear)"</t>
+  </si>
+  <si>
+    <t>"Volume 3 - Apoio ao Diagnóstico e à Terapia (Imagenologia)"</t>
+  </si>
+  <si>
+    <t>"Volume 2 - Internação e Apoio ao Diagnóstico e à Terapia (Reabilitação)"</t>
   </si>
 </sst>
 </file>
@@ -988,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1061,12 +1067,6 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1161,39 +1161,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -1268,6 +1236,22 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1305,30 +1289,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1734,58 +1694,58 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="10.3" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="10.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.3828125" customWidth="1"/>
     <col min="2" max="2" width="33.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.55" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="37" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="35" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>98</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -1793,11 +1753,11 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -1805,232 +1765,232 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C9" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C12" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C13" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C14" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C15" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C16" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C17" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46139.487102199077</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>46214.363713541665</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C20" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>173</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>_xlfn.TRANSLATE(B21,"pt","es")</f>
         <v>Cuaderno SomaSUS preparado por el Sistema Unificado de Salud de Brasil</v>
       </c>
-      <c r="C22" s="38" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C22" s="36" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Cuaderno SomaSUS prepared by the Unified Health System of Brazil</v>
       </c>
-      <c r="C23" s="38" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C23" s="36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>168</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="38" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C25" s="36" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize the SomaSUS Notebook prepared by the Unified Health System of Brazil.</v>
       </c>
-      <c r="C26" s="38" t="s">
-        <v>177</v>
+      <c r="C26" s="36" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2059,2537 +2019,2530 @@
     <col min="17" max="17" width="38.69140625" style="1" customWidth="1"/>
     <col min="18" max="18" width="4.15234375" style="1" customWidth="1"/>
     <col min="19" max="19" width="11.69140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.4609375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.921875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="8.921875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.3828125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.84375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="8.84375" style="1" customWidth="1"/>
     <col min="23" max="23" width="6.3828125" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.23046875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="21.3046875" style="1" customWidth="1"/>
     <col min="25" max="25" width="8.84375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.4609375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9.3828125" style="1" customWidth="1"/>
     <col min="27" max="27" width="49.69140625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="L1" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="S1" s="30" t="s">
+      <c r="R1" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="S1" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="T1" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="U1" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="V1" s="30" t="s">
+      <c r="V1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="56" t="s">
+      <c r="W1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="X1" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y1" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z1" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA1" s="41" t="s">
-        <v>170</v>
+      <c r="X1" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y1" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z1" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA1" s="39" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="42">
+      <c r="A2" s="40">
         <v>2</v>
       </c>
-      <c r="B2" s="48" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>185</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>203</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="44" t="str">
+      <c r="B2" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="42" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
         <v>Contêiner</v>
       </c>
-      <c r="M2" s="44" t="str">
+      <c r="M2" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N2" s="44" t="str">
+      <c r="N2" s="42" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
         <v>Definida</v>
       </c>
-      <c r="O2" s="44" t="str">
+      <c r="O2" s="42" t="str">
         <f t="shared" si="1"/>
         <v>No Projeto</v>
       </c>
-      <c r="P2" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q2" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="R2" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="47" t="str">
+      <c r="P2" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q2" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="R2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="45" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
         <v>Contêiner</v>
       </c>
-      <c r="T2" s="47" t="str">
+      <c r="T2" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U2" s="47" t="str">
+      <c r="U2" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Definida</v>
       </c>
-      <c r="V2" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W2" s="57" t="str">
+      <c r="V2" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W2" s="55" t="str">
         <f>CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
-      <c r="X2" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="45" t="str">
+      <c r="X2" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="43" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
     <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="42">
+      <c r="A3" s="40">
         <v>3</v>
       </c>
-      <c r="B3" s="48" t="s">
-        <v>202</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="44" t="str">
+      <c r="B3" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Contêiner</v>
       </c>
-      <c r="M3" s="44" t="str">
+      <c r="M3" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N3" s="44" t="str">
+      <c r="N3" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requerida</v>
       </c>
-      <c r="O3" s="44" t="str">
+      <c r="O3" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
-      <c r="P3" s="45" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q3" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="47" t="str">
+      <c r="P3" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q3" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="R3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Contêiner</v>
       </c>
-      <c r="T3" s="47" t="str">
+      <c r="T3" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U3" s="47" t="str">
+      <c r="U3" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Requerida</v>
       </c>
-      <c r="V3" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W3" s="57" t="str">
+      <c r="V3" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W3" s="55" t="str">
         <f t="shared" ref="W3:W27" si="4">CONCATENATE("Key-SUS-",A3)</f>
         <v>Key-SUS-3</v>
       </c>
-      <c r="X3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="45" t="str">
+      <c r="X3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="43" t="str">
         <f t="shared" si="3"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
     <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="42">
+      <c r="A4" s="40">
         <v>4</v>
       </c>
-      <c r="B4" s="48" t="s">
-        <v>202</v>
-      </c>
-      <c r="C4" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>187</v>
-      </c>
-      <c r="F4" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="44" t="str">
+      <c r="B4" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Contêiner</v>
       </c>
-      <c r="M4" s="44" t="str">
+      <c r="M4" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N4" s="44" t="str">
+      <c r="N4" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requerida</v>
       </c>
-      <c r="O4" s="44" t="str">
+      <c r="O4" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
-      <c r="P4" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q4" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="R4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="47" t="str">
+      <c r="P4" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q4" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="R4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Contêiner</v>
       </c>
-      <c r="T4" s="47" t="str">
+      <c r="T4" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U4" s="47" t="str">
+      <c r="U4" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Requerida</v>
       </c>
-      <c r="V4" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W4" s="57" t="str">
+      <c r="V4" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W4" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-4</v>
       </c>
-      <c r="X4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="45" t="str">
+      <c r="X4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="43" t="str">
         <f t="shared" si="3"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
     <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="42">
+      <c r="A5" s="40">
         <v>5</v>
       </c>
-      <c r="B5" s="48" t="s">
-        <v>202</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" s="49" t="s">
-        <v>208</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="44" t="str">
+      <c r="B5" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Contêiner</v>
       </c>
-      <c r="M5" s="44" t="str">
+      <c r="M5" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N5" s="44" t="str">
+      <c r="N5" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requerida</v>
       </c>
-      <c r="O5" s="44" t="str">
+      <c r="O5" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
-      <c r="P5" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q5" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="R5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="47" t="str">
+      <c r="P5" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q5" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="R5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Contêiner</v>
       </c>
-      <c r="T5" s="47" t="str">
+      <c r="T5" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U5" s="47" t="str">
+      <c r="U5" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Requerida</v>
       </c>
-      <c r="V5" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W5" s="57" t="str">
+      <c r="V5" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W5" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-5</v>
       </c>
-      <c r="X5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="45" t="str">
+      <c r="X5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="43" t="str">
         <f t="shared" si="3"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
     <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="42">
+      <c r="A6" s="40">
         <v>6</v>
       </c>
-      <c r="B6" s="48" t="s">
-        <v>202</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>187</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>210</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="44" t="str">
+      <c r="B6" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Contêiner</v>
       </c>
-      <c r="M6" s="44" t="str">
+      <c r="M6" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N6" s="44" t="str">
+      <c r="N6" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requerida</v>
       </c>
-      <c r="O6" s="44" t="str">
+      <c r="O6" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
-      <c r="P6" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q6" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="R6" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="47" t="str">
+      <c r="P6" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q6" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="R6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Contêiner</v>
       </c>
-      <c r="T6" s="47" t="str">
+      <c r="T6" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U6" s="47" t="str">
+      <c r="U6" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Requerida</v>
       </c>
-      <c r="V6" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W6" s="57" t="str">
+      <c r="V6" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W6" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-6</v>
       </c>
-      <c r="X6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="45" t="str">
+      <c r="X6" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="43" t="str">
         <f t="shared" si="3"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="42">
+      <c r="A7" s="40">
         <v>7</v>
       </c>
-      <c r="B7" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="50" t="s">
+      <c r="B7" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="44" t="str">
+      <c r="F7" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="42" t="str">
         <f t="shared" ref="L7:N26" si="5">CONCATENATE("", C7)</f>
         <v>SUS</v>
       </c>
-      <c r="M7" s="44" t="str">
+      <c r="M7" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Caderno</v>
       </c>
-      <c r="N7" s="44" t="str">
+      <c r="N7" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SomaSUS</v>
       </c>
-      <c r="O7" s="44" t="str">
+      <c r="O7" s="42" t="str">
         <f t="shared" ref="O7:O27" si="6">F7</f>
         <v>SUS.Volume</v>
       </c>
-      <c r="P7" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q7" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="R7" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="44" t="str">
+      <c r="P7" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q7" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="R7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="42" t="str">
         <f t="shared" ref="S7:U26" si="7">SUBSTITUTE(D7, "_", " ")</f>
         <v>SUS.Caderno</v>
       </c>
-      <c r="T7" s="44" t="str">
+      <c r="T7" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SomaSUS</v>
       </c>
-      <c r="U7" s="44" t="str">
+      <c r="U7" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Volume</v>
       </c>
-      <c r="V7" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W7" s="57" t="str">
+      <c r="V7" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W7" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-7</v>
       </c>
-      <c r="X7" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y7" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z7" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="AA7" s="45" t="str">
+      <c r="X7" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA7" s="43" t="str">
         <f t="shared" ref="AA7:AA27" si="8">_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="42">
+      <c r="A8" s="40">
         <v>8</v>
       </c>
-      <c r="B8" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="44" t="str">
+      <c r="B8" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F8" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M8" s="44" t="str">
+      <c r="M8" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N8" s="44" t="str">
+      <c r="N8" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O8" s="44" t="str">
+      <c r="O8" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Area</v>
       </c>
-      <c r="P8" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="R8" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="44" t="str">
+      <c r="P8" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="R8" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T8" s="44" t="str">
+      <c r="T8" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U8" s="44" t="str">
+      <c r="U8" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Area</v>
       </c>
-      <c r="V8" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W8" s="57" t="str">
+      <c r="V8" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W8" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-8</v>
       </c>
-      <c r="X8" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y8" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z8" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA8" s="45" t="str">
+      <c r="X8" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y8" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z8" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA8" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to an environment that is not totally cloistered.</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42">
+      <c r="A9" s="40">
         <v>9</v>
       </c>
-      <c r="B9" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="44" t="str">
+      <c r="B9" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M9" s="44" t="str">
+      <c r="M9" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N9" s="44" t="str">
+      <c r="N9" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O9" s="44" t="str">
+      <c r="O9" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Box</v>
       </c>
-      <c r="P9" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q9" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="R9" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="44" t="str">
+      <c r="P9" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q9" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="R9" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T9" s="44" t="str">
+      <c r="T9" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U9" s="44" t="str">
+      <c r="U9" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Box</v>
       </c>
-      <c r="V9" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W9" s="57" t="str">
+      <c r="V9" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W9" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-9</v>
       </c>
-      <c r="X9" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y9" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z9" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA9" s="45" t="str">
+      <c r="X9" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y9" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z9" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA9" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a closed and small environment, usually to serve patients.</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="42">
+      <c r="A10" s="40">
         <v>10</v>
       </c>
-      <c r="B10" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F10" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="G10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="44" t="str">
+      <c r="B10" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M10" s="44" t="str">
+      <c r="M10" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N10" s="44" t="str">
+      <c r="N10" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O10" s="44" t="str">
+      <c r="O10" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="P10" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q10" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="R10" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="44" t="str">
+      <c r="P10" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q10" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="R10" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T10" s="44" t="str">
+      <c r="T10" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U10" s="44" t="str">
+      <c r="U10" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="V10" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W10" s="57" t="str">
+      <c r="V10" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W10" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-10</v>
       </c>
-      <c r="X10" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y10" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z10" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA10" s="45" t="str">
+      <c r="X10" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y10" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z10" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA10" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a doctor's office-type environment.</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="42">
+      <c r="A11" s="40">
         <v>11</v>
       </c>
-      <c r="B11" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="44" t="str">
+      <c r="B11" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M11" s="44" t="str">
+      <c r="M11" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N11" s="44" t="str">
+      <c r="N11" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O11" s="44" t="str">
+      <c r="O11" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="P11" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q11" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="R11" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="44" t="str">
+      <c r="P11" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q11" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="R11" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T11" s="44" t="str">
+      <c r="T11" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U11" s="44" t="str">
+      <c r="U11" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="V11" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W11" s="57" t="str">
+      <c r="V11" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W11" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-11</v>
       </c>
-      <c r="X11" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y11" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z11" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA11" s="45" t="str">
+      <c r="X11" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y11" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z11" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA11" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to an environment equipped to fulfill ward functions.</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42">
+      <c r="A12" s="40">
         <v>12</v>
       </c>
-      <c r="B12" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F12" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="44" t="str">
+      <c r="B12" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M12" s="44" t="str">
+      <c r="M12" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N12" s="44" t="str">
+      <c r="N12" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O12" s="44" t="str">
+      <c r="O12" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="P12" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q12" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="R12" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="44" t="str">
+      <c r="P12" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q12" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="R12" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T12" s="44" t="str">
+      <c r="T12" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U12" s="44" t="str">
+      <c r="U12" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="V12" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W12" s="57" t="str">
+      <c r="V12" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W12" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-12</v>
       </c>
-      <c r="X12" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y12" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z12" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA12" s="45" t="str">
+      <c r="X12" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y12" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z12" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA12" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to an environment equipped to perform laboratory functions.</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="42">
+      <c r="A13" s="40">
         <v>13</v>
       </c>
-      <c r="B13" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F13" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="G13" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="44" t="str">
+      <c r="B13" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M13" s="44" t="str">
+      <c r="M13" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N13" s="44" t="str">
+      <c r="N13" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O13" s="44" t="str">
+      <c r="O13" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="P13" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q13" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="R13" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="44" t="str">
+      <c r="P13" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q13" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="R13" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T13" s="44" t="str">
+      <c r="T13" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U13" s="44" t="str">
+      <c r="U13" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="V13" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W13" s="57" t="str">
+      <c r="V13" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W13" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-13</v>
       </c>
-      <c r="X13" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y13" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z13" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA13" s="45" t="str">
+      <c r="X13" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y13" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z13" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA13" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a closed or open environment for medical treatment pools.</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="42">
+      <c r="A14" s="40">
         <v>14</v>
       </c>
-      <c r="B14" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E14" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="44" t="str">
+      <c r="B14" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M14" s="44" t="str">
+      <c r="M14" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N14" s="44" t="str">
+      <c r="N14" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O14" s="44" t="str">
+      <c r="O14" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="P14" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q14" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="R14" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="44" t="str">
+      <c r="P14" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q14" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="R14" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T14" s="44" t="str">
+      <c r="T14" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U14" s="44" t="str">
+      <c r="U14" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="V14" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W14" s="57" t="str">
+      <c r="V14" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W14" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-14</v>
       </c>
-      <c r="X14" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y14" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z14" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA14" s="45" t="str">
+      <c r="X14" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y14" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z14" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA14" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a nursing station associated with an infirmary.</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42">
+      <c r="A15" s="40">
         <v>15</v>
       </c>
-      <c r="B15" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F15" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G15" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="44" t="str">
+      <c r="B15" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M15" s="44" t="str">
+      <c r="M15" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N15" s="44" t="str">
+      <c r="N15" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O15" s="44" t="str">
+      <c r="O15" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="P15" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q15" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="R15" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="44" t="str">
+      <c r="P15" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q15" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="R15" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T15" s="44" t="str">
+      <c r="T15" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U15" s="44" t="str">
+      <c r="U15" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="V15" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W15" s="57" t="str">
+      <c r="V15" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W15" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-15</v>
       </c>
-      <c r="X15" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y15" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z15" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA15" s="45" t="str">
+      <c r="X15" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y15" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z15" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA15" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a hospitalization room.</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="42">
+      <c r="A16" s="40">
         <v>16</v>
       </c>
-      <c r="B16" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L16" s="44" t="str">
+      <c r="B16" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M16" s="44" t="str">
+      <c r="M16" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N16" s="44" t="str">
+      <c r="N16" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O16" s="44" t="str">
+      <c r="O16" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="P16" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q16" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="R16" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="44" t="str">
+      <c r="P16" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q16" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="R16" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T16" s="44" t="str">
+      <c r="T16" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U16" s="44" t="str">
+      <c r="U16" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="V16" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W16" s="57" t="str">
+      <c r="V16" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W16" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-16</v>
       </c>
-      <c r="X16" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y16" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z16" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA16" s="45" t="str">
+      <c r="X16" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y16" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z16" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA16" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a room to function as administrative or technical service.</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="42">
+      <c r="A17" s="40">
         <v>17</v>
       </c>
-      <c r="B17" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="F17" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="44" t="str">
+      <c r="B17" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M17" s="44" t="str">
+      <c r="M17" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N17" s="44" t="str">
+      <c r="N17" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O17" s="44" t="str">
+      <c r="O17" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="P17" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q17" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="R17" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="44" t="str">
+      <c r="P17" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q17" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="R17" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T17" s="44" t="str">
+      <c r="T17" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="U17" s="44" t="str">
+      <c r="U17" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="V17" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W17" s="57" t="str">
+      <c r="V17" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W17" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-17</v>
       </c>
-      <c r="X17" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y17" s="45" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z17" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA17" s="45" t="str">
+      <c r="X17" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y17" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="Z17" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA17" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a defined zoning.</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42">
+      <c r="A18" s="40">
         <v>18</v>
       </c>
-      <c r="B18" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="55" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="44" t="str">
+      <c r="B18" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M18" s="44" t="str">
+      <c r="M18" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N18" s="44" t="str">
+      <c r="N18" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O18" s="44" t="str">
+      <c r="O18" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="P18" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q18" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="R18" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="44" t="str">
+      <c r="P18" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q18" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="R18" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T18" s="44" t="str">
+      <c r="T18" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="U18" s="44" t="str">
+      <c r="U18" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="V18" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W18" s="57" t="str">
+      <c r="V18" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W18" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-18</v>
       </c>
-      <c r="X18" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y18" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z18" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA18" s="45" t="str">
+      <c r="X18" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="AA18" s="43" t="str">
         <f t="shared" si="8"/>
         <v>They are the functional units of the Unified Health System of Brazil.</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="42">
+      <c r="A19" s="40">
         <v>19</v>
       </c>
-      <c r="B19" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="F19" s="55" t="s">
+      <c r="B19" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="G19" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L19" s="44" t="str">
+      <c r="D19" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M19" s="44" t="str">
+      <c r="M19" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N19" s="44" t="str">
+      <c r="N19" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O19" s="44" t="str">
+      <c r="O19" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="P19" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q19" s="44" t="s">
-        <v>152</v>
-      </c>
-      <c r="R19" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="44" t="str">
+      <c r="P19" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q19" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="R19" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T19" s="44" t="str">
+      <c r="T19" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="U19" s="44" t="str">
+      <c r="U19" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="V19" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W19" s="57" t="str">
+      <c r="V19" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W19" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-19</v>
       </c>
-      <c r="X19" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y19" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z19" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA19" s="45" t="str">
+      <c r="X19" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="AA19" s="43" t="str">
         <f t="shared" si="8"/>
         <v>They are the Sectors of the Unified Health System of Brazil.</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="42">
+      <c r="A20" s="40">
         <v>20</v>
       </c>
-      <c r="B20" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" s="55" t="s">
-        <v>161</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="44" t="str">
+      <c r="B20" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M20" s="44" t="str">
+      <c r="M20" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N20" s="44" t="str">
+      <c r="N20" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O20" s="44" t="str">
+      <c r="O20" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="P20" s="44" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q20" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="R20" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S20" s="44" t="str">
+      <c r="P20" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q20" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="R20" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S20" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="T20" s="44" t="str">
+      <c r="T20" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="U20" s="44" t="str">
+      <c r="U20" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="V20" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W20" s="57" t="str">
+      <c r="V20" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W20" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-20</v>
       </c>
-      <c r="X20" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y20" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z20" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA20" s="45" t="str">
+      <c r="X20" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y20" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z20" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA20" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42">
+      <c r="A21" s="40">
         <v>21</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" s="55" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="44" t="str">
+      <c r="G21" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M21" s="44" t="str">
+      <c r="M21" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N21" s="44" t="str">
+      <c r="N21" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O21" s="44" t="str">
+      <c r="O21" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="P21" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q21" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="R21" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S21" s="44" t="str">
+      <c r="P21" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q21" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="R21" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S21" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="T21" s="44" t="str">
+      <c r="T21" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="U21" s="44" t="str">
+      <c r="U21" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="V21" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W21" s="57" t="str">
+      <c r="V21" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W21" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-21</v>
       </c>
-      <c r="X21" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y21" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z21" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA21" s="45" t="str">
+      <c r="X21" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y21" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z21" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA21" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="42">
+      <c r="A22" s="40">
         <v>22</v>
       </c>
-      <c r="B22" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F22" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="G22" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L22" s="44" t="str">
+      <c r="B22" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M22" s="44" t="str">
+      <c r="M22" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N22" s="44" t="str">
+      <c r="N22" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O22" s="44" t="str">
+      <c r="O22" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="P22" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q22" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="R22" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S22" s="44" t="str">
+      <c r="P22" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q22" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="R22" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S22" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="T22" s="44" t="str">
+      <c r="T22" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="U22" s="44" t="str">
+      <c r="U22" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="V22" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W22" s="57" t="str">
+      <c r="V22" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W22" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-22</v>
       </c>
-      <c r="X22" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y22" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z22" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA22" s="45" t="str">
+      <c r="X22" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y22" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z22" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA22" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42">
+      <c r="A23" s="40">
         <v>23</v>
       </c>
-      <c r="B23" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F23" s="55" t="s">
-        <v>153</v>
-      </c>
-      <c r="G23" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L23" s="44" t="str">
+      <c r="B23" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M23" s="44" t="str">
+      <c r="M23" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N23" s="44" t="str">
+      <c r="N23" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O23" s="44" t="str">
+      <c r="O23" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="P23" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q23" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="R23" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S23" s="44" t="str">
+      <c r="P23" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q23" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="R23" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S23" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="T23" s="44" t="str">
+      <c r="T23" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="U23" s="44" t="str">
+      <c r="U23" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="V23" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W23" s="57" t="str">
+      <c r="V23" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W23" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-23</v>
       </c>
-      <c r="X23" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y23" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z23" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA23" s="45" t="str">
+      <c r="X23" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y23" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z23" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA23" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
     <row r="24" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="42">
+      <c r="A24" s="40">
         <v>24</v>
       </c>
-      <c r="B24" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F24" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="G24" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K24" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="44" t="str">
+      <c r="B24" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M24" s="44" t="str">
+      <c r="M24" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N24" s="44" t="str">
+      <c r="N24" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O24" s="44" t="str">
+      <c r="O24" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="P24" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q24" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="R24" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S24" s="44" t="str">
+      <c r="P24" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q24" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="R24" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S24" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="T24" s="44" t="str">
+      <c r="T24" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="U24" s="44" t="str">
+      <c r="U24" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="V24" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W24" s="57" t="str">
+      <c r="V24" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W24" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-24</v>
       </c>
-      <c r="X24" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y24" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z24" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA24" s="45" t="str">
+      <c r="X24" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y24" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z24" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA24" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
     <row r="25" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="42">
+      <c r="A25" s="40">
         <v>25</v>
       </c>
-      <c r="B25" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="F25" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L25" s="44" t="str">
+      <c r="B25" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M25" s="44" t="str">
+      <c r="M25" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N25" s="44" t="str">
+      <c r="N25" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O25" s="44" t="str">
+      <c r="O25" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="P25" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q25" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="R25" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S25" s="44" t="str">
+      <c r="P25" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q25" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="R25" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S25" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="T25" s="44" t="str">
+      <c r="T25" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="U25" s="44" t="str">
+      <c r="U25" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="V25" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W25" s="57" t="str">
+      <c r="V25" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W25" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-25</v>
       </c>
-      <c r="X25" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y25" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z25" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA25" s="45" t="str">
+      <c r="X25" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y25" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z25" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA25" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
     <row r="26" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="42">
+      <c r="A26" s="40">
         <v>26</v>
       </c>
-      <c r="B26" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="F26" s="55" t="s">
-        <v>169</v>
-      </c>
-      <c r="G26" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K26" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L26" s="44" t="str">
+      <c r="B26" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="G26" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS</v>
       </c>
-      <c r="M26" s="44" t="str">
+      <c r="M26" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N26" s="44" t="str">
+      <c r="N26" s="42" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O26" s="44" t="str">
+      <c r="O26" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="P26" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q26" s="44" t="s">
-        <v>157</v>
-      </c>
-      <c r="R26" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S26" s="44" t="str">
+      <c r="P26" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q26" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="R26" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S26" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="T26" s="44" t="str">
+      <c r="T26" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="U26" s="44" t="str">
+      <c r="U26" s="42" t="str">
         <f t="shared" si="7"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="V26" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W26" s="57" t="str">
+      <c r="V26" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W26" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-26</v>
       </c>
-      <c r="X26" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y26" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z26" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA26" s="45" t="str">
+      <c r="X26" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y26" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z26" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA26" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
     <row r="27" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="42">
+      <c r="A27" s="40">
         <v>27</v>
       </c>
-      <c r="B27" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="F27" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="G27" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K27" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L27" s="44" t="str">
+      <c r="B27" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="42" t="str">
         <f t="shared" ref="L27:N27" si="9">CONCATENATE("", C27)</f>
         <v>SUS</v>
       </c>
-      <c r="M27" s="44" t="str">
+      <c r="M27" s="42" t="str">
         <f t="shared" si="9"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N27" s="44" t="str">
+      <c r="N27" s="42" t="str">
         <f t="shared" si="9"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O27" s="44" t="str">
+      <c r="O27" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="P27" s="44" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q27" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="R27" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S27" s="44" t="str">
+      <c r="P27" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q27" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="R27" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S27" s="42" t="str">
         <f t="shared" ref="S27:U27" si="10">SUBSTITUTE(D27, "_", " ")</f>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="T27" s="44" t="str">
+      <c r="T27" s="42" t="str">
         <f t="shared" si="10"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="U27" s="44" t="str">
+      <c r="U27" s="42" t="str">
         <f t="shared" si="10"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="V27" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="W27" s="57" t="str">
+      <c r="V27" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="W27" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-SUS-27</v>
       </c>
-      <c r="X27" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y27" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z27" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA27" s="45" t="str">
+      <c r="X27" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y27" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z27" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA27" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Elements for feeding used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D7:F27 L7:Q27">
-    <cfRule type="cellIs" dxfId="27" priority="16" operator="equal">
+  <conditionalFormatting sqref="A2:A27">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F23">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S7:U27 X7:XFD27 V2:V27">
-    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1">
-    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A27">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="D7:F27 L7:Q27">
+    <cfRule type="cellIs" dxfId="22" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+  <conditionalFormatting sqref="F7:F23">
+    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F27">
+    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V27 Z7:XFD7 S7:U27 X8:XFD17 Z18:XFD19 X20:XFD27">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA6">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4616,72 +4569,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="Q1" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="33" t="s">
+      <c r="T1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="33" t="s">
+      <c r="U1" s="31" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32">
+      <c r="A2" s="30">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -4748,7 +4701,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4776,10 +4729,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -4795,7 +4748,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4806,35 +4759,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.61328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.61328125" customWidth="1"/>
-    <col min="4" max="4" width="2.3828125" style="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.84375" style="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.3828125" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.84375" style="35" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.3828125" style="35" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.15234375" style="35" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.61328125" style="35" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.84375" style="35" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.3828125" style="22" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.84375" style="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4" style="22" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="47.53515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="2.84375" style="35" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.84375" style="35" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.84375" style="35" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.3828125" style="35" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2.84375" style="35" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.3828125" style="35" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="2.84375" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.3828125" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.84375" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.69140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.53515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.765625" style="33" customWidth="1"/>
+    <col min="13" max="13" width="6.07421875" style="33" customWidth="1"/>
+    <col min="14" max="14" width="2.3828125" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.84375" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -4850,10 +4795,10 @@
       <c r="E1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="21" t="s">
         <v>48</v>
       </c>
       <c r="H1" s="20" t="s">
@@ -4863,49 +4808,25 @@
         <v>48</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="S1" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="T1" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="U1" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="V1" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="W1" s="20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -4913,70 +4834,46 @@
         <v>78</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="O2" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="P2" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q2" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="R2" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="S2" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="T2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E2" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="N2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -4984,70 +4881,46 @@
         <v>79</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="O3" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="P3" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q3" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="R3" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="S3" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="T3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W3" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G3" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="N3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -5055,70 +4928,46 @@
         <v>80</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="J4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="O4" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="P4" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q4" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="R4" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="S4" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="T4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="L4" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -5126,117 +4975,78 @@
         <v>81</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="J5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="O5" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="P5" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q5" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="R5" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="S5" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="N5" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="32" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8BA023-242B-48B0-B325-4E669396DC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA3B5E3-ED5E-4EF9-BBF6-D6A9F566D273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -340,9 +340,6 @@
     <t>Interop</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>SUS.Area</t>
   </si>
   <si>
@@ -607,9 +604,6 @@
     <t>Aviso</t>
   </si>
   <si>
-    <t>"-"</t>
-  </si>
-  <si>
     <t>categoria.revit</t>
   </si>
   <si>
@@ -622,15 +616,9 @@
     <t>Alert</t>
   </si>
   <si>
-    <t>Definida</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
     <t>[ 5I.10.54.12.16 ]</t>
   </si>
   <si>
@@ -676,9 +664,6 @@
     <t>Gestão</t>
   </si>
   <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Requisito.Espacial</t>
   </si>
   <si>
@@ -725,6 +710,21 @@
   </si>
   <si>
     <t>"Volume 2 - Internação e Apoio ao Diagnóstico e à Terapia (Reabilitação)"</t>
+  </si>
+  <si>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>Arquitetura</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>"[ - ]"</t>
   </si>
 </sst>
 </file>
@@ -932,13 +932,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor theme="0"/>
       </patternFill>
     </fill>
@@ -994,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1151,17 +1151,74 @@
     <xf numFmtId="0" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="30">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1694,14 +1751,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="10.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.3828125" customWidth="1"/>
-    <col min="2" max="2" width="33.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
@@ -1709,21 +1766,21 @@
         <v>48</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
@@ -1731,10 +1788,10 @@
         <v>77</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -1742,10 +1799,10 @@
         <v>25</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -1754,10 +1811,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -1766,10 +1823,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -1777,21 +1834,21 @@
         <v>55</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -1799,10 +1856,10 @@
         <v>58</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -1810,10 +1867,10 @@
         <v>60</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -1821,10 +1878,10 @@
         <v>60</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -1832,10 +1889,10 @@
         <v>60</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -1843,10 +1900,10 @@
         <v>82</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -1854,10 +1911,10 @@
         <v>60</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -1865,10 +1922,10 @@
         <v>60</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -1876,10 +1933,10 @@
         <v>60</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -1887,22 +1944,22 @@
         <v>68</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46214.363713541665</v>
+        <v>46216.346035648145</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
@@ -1910,10 +1967,10 @@
         <v>60</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -1921,56 +1978,56 @@
         <v>60</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B21" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
         <v>173</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="14" t="s">
-        <v>174</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>_xlfn.TRANSLATE(B21,"pt","es")</f>
         <v>Cuaderno SomaSUS preparado por el Sistema Unificado de Salud de Brasil</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Cuaderno SomaSUS prepared by the Unified Health System of Brazil</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
@@ -1978,19 +2035,19 @@
         <v>74</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize the SomaSUS Notebook prepared by the Unified Health System of Brazil.</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2002,35 +2059,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3828125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="5.53515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.15234375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.15234375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.15234375" style="1" customWidth="1"/>
-    <col min="7" max="11" width="6.84375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" style="1" customWidth="1"/>
+    <col min="7" max="11" width="6.85546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.15234375" style="8" customWidth="1"/>
-    <col min="14" max="14" width="9.3046875" style="8" customWidth="1"/>
-    <col min="15" max="15" width="10.84375" style="8" customWidth="1"/>
-    <col min="16" max="16" width="37.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="38.69140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="4.15234375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.69140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.3828125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.84375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="8.84375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.3828125" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.3046875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.84375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.3828125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="49.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.84375" style="1"/>
+    <col min="13" max="13" width="11.140625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" style="8" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="37.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="38.7109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="4.140625" style="54" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.42578125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="8.85546875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.28515625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.85546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9.42578125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="49.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -2097,40 +2154,40 @@
       <c r="V1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="54" t="s">
+      <c r="W1" s="55" t="s">
         <v>0</v>
       </c>
       <c r="X1" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y1" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="Y1" s="28" t="s">
+      <c r="Z1" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="Z1" s="28" t="s">
-        <v>101</v>
-      </c>
       <c r="AA1" s="39" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40">
         <v>2</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>131</v>
+        <v>210</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>193</v>
       </c>
       <c r="D2" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>130</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>198</v>
       </c>
       <c r="G2" s="41" t="s">
         <v>1</v>
@@ -2149,7 +2206,7 @@
       </c>
       <c r="L2" s="42" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M2" s="42" t="str">
         <f t="shared" si="0"/>
@@ -2157,24 +2214,24 @@
       </c>
       <c r="N2" s="42" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O2" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
+        <v>Contêiner</v>
       </c>
       <c r="P2" s="43" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q2" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="R2" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="R2" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S2" s="45" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="T2" s="45" t="str">
         <f t="shared" si="2"/>
@@ -2182,13 +2239,13 @@
       </c>
       <c r="U2" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="V2" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W2" s="55" t="str">
-        <f>CONCATENATE("Key-SUS-",A2)</f>
+        <v>212</v>
+      </c>
+      <c r="W2" s="56" t="str">
+        <f t="shared" ref="W2:W27" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
       <c r="X2" s="43" t="s">
@@ -2198,31 +2255,31 @@
         <v>1</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="AA2" s="43" t="str">
-        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="40">
         <v>3</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>131</v>
+        <v>210</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>193</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="E3" s="46" t="s">
-        <v>182</v>
+        <v>129</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>211</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G3" s="41" t="s">
         <v>1</v>
@@ -2241,7 +2298,7 @@
       </c>
       <c r="L3" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M3" s="42" t="str">
         <f t="shared" si="0"/>
@@ -2249,24 +2306,24 @@
       </c>
       <c r="N3" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O3" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="43" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="Q3" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="R3" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="R3" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S3" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="T3" s="45" t="str">
         <f t="shared" si="2"/>
@@ -2274,47 +2331,47 @@
       </c>
       <c r="U3" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="V3" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W3" s="55" t="str">
-        <f t="shared" ref="W3:W27" si="4">CONCATENATE("Key-SUS-",A3)</f>
+        <v>212</v>
+      </c>
+      <c r="W3" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-3</v>
       </c>
       <c r="X3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="Y3" s="43" t="s">
+      <c r="Y3" s="45" t="s">
         <v>1</v>
       </c>
       <c r="Z3" s="44" t="s">
         <v>1</v>
       </c>
       <c r="AA3" s="43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40">
         <v>4</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>131</v>
+        <v>210</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>193</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>182</v>
+        <v>129</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>211</v>
       </c>
       <c r="F4" s="47" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G4" s="41" t="s">
         <v>1</v>
@@ -2333,7 +2390,7 @@
       </c>
       <c r="L4" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M4" s="42" t="str">
         <f t="shared" si="0"/>
@@ -2341,24 +2398,24 @@
       </c>
       <c r="N4" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O4" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="43" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="Q4" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="R4" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="R4" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S4" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="T4" s="45" t="str">
         <f t="shared" si="2"/>
@@ -2366,47 +2423,47 @@
       </c>
       <c r="U4" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="V4" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W4" s="55" t="str">
+        <v>212</v>
+      </c>
+      <c r="W4" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-SUS-4</v>
+      </c>
+      <c r="X4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="43" t="str">
         <f t="shared" si="4"/>
-        <v>Key-SUS-4</v>
-      </c>
-      <c r="X4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="43" t="str">
-        <f t="shared" si="3"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="40">
         <v>5</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>131</v>
+        <v>210</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>193</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>182</v>
+        <v>129</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>211</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G5" s="41" t="s">
         <v>1</v>
@@ -2425,7 +2482,7 @@
       </c>
       <c r="L5" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M5" s="42" t="str">
         <f t="shared" si="0"/>
@@ -2433,24 +2490,24 @@
       </c>
       <c r="N5" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O5" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="43" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="Q5" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="R5" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="R5" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S5" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="T5" s="45" t="str">
         <f t="shared" si="2"/>
@@ -2458,47 +2515,47 @@
       </c>
       <c r="U5" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="V5" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W5" s="55" t="str">
+        <v>212</v>
+      </c>
+      <c r="W5" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-SUS-5</v>
+      </c>
+      <c r="X5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="43" t="str">
         <f t="shared" si="4"/>
-        <v>Key-SUS-5</v>
-      </c>
-      <c r="X5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="43" t="str">
-        <f t="shared" si="3"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
         <v>6</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>131</v>
+        <v>210</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>193</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>182</v>
+        <v>129</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>211</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G6" s="41" t="s">
         <v>1</v>
@@ -2517,7 +2574,7 @@
       </c>
       <c r="L6" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M6" s="42" t="str">
         <f t="shared" si="0"/>
@@ -2525,24 +2582,24 @@
       </c>
       <c r="N6" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O6" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="43" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="Q6" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="R6" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="R6" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S6" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="T6" s="45" t="str">
         <f t="shared" si="2"/>
@@ -2550,47 +2607,47 @@
       </c>
       <c r="U6" s="45" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="V6" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W6" s="55" t="str">
+        <v>212</v>
+      </c>
+      <c r="W6" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-SUS-6</v>
+      </c>
+      <c r="X6" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="43" t="str">
         <f t="shared" si="4"/>
-        <v>Key-SUS-6</v>
-      </c>
-      <c r="X6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="43" t="str">
-        <f t="shared" si="3"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="40">
         <v>7</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G7" s="41" t="s">
         <v>1</v>
@@ -2624,12 +2681,12 @@
         <v>SUS.Volume</v>
       </c>
       <c r="P7" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q7" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="Q7" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="R7" s="44" t="s">
+      <c r="R7" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S7" s="42" t="str">
@@ -2645,10 +2702,10 @@
         <v>SUS.Volume</v>
       </c>
       <c r="V7" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W7" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W7" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-7</v>
       </c>
       <c r="X7" s="43" t="s">
@@ -2658,31 +2715,31 @@
         <v>1</v>
       </c>
       <c r="Z7" s="44" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AA7" s="43" t="str">
         <f t="shared" ref="AA7:AA27" si="8">_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="40">
         <v>8</v>
       </c>
       <c r="B8" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="51" t="s">
         <v>86</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>87</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>1</v>
@@ -2716,12 +2773,12 @@
         <v>SUS.Area</v>
       </c>
       <c r="P8" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q8" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="Q8" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="R8" s="44" t="s">
+      <c r="R8" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="42" t="str">
@@ -2737,44 +2794,44 @@
         <v>SUS.Area</v>
       </c>
       <c r="V8" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W8" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W8" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-8</v>
       </c>
       <c r="X8" s="43" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y8" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z8" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA8" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to an environment that is not totally cloistered.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="40">
         <v>9</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E9" s="50" t="s">
-        <v>135</v>
-      </c>
       <c r="F9" s="51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G9" s="41" t="s">
         <v>1</v>
@@ -2808,12 +2865,12 @@
         <v>SUS.Box</v>
       </c>
       <c r="P9" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q9" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="Q9" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="R9" s="44" t="s">
+      <c r="R9" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S9" s="42" t="str">
@@ -2829,44 +2886,44 @@
         <v>SUS.Box</v>
       </c>
       <c r="V9" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W9" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W9" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-9</v>
       </c>
       <c r="X9" s="43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y9" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z9" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA9" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a closed and small environment, usually to serve patients.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="40">
         <v>10</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E10" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="50" t="s">
-        <v>135</v>
-      </c>
       <c r="F10" s="51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G10" s="41" t="s">
         <v>1</v>
@@ -2900,12 +2957,12 @@
         <v>SUS.Consultório</v>
       </c>
       <c r="P10" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q10" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="Q10" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R10" s="44" t="s">
+      <c r="R10" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S10" s="42" t="str">
@@ -2921,44 +2978,44 @@
         <v>SUS.Consultório</v>
       </c>
       <c r="V10" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W10" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W10" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-10</v>
       </c>
       <c r="X10" s="43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y10" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z10" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA10" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a doctor's office-type environment.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="40">
         <v>11</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E11" s="50" t="s">
-        <v>135</v>
-      </c>
       <c r="F11" s="51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G11" s="41" t="s">
         <v>1</v>
@@ -2992,12 +3049,12 @@
         <v>SUS.Enfermaria</v>
       </c>
       <c r="P11" s="42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q11" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="R11" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="R11" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S11" s="42" t="str">
@@ -3013,44 +3070,44 @@
         <v>SUS.Enfermaria</v>
       </c>
       <c r="V11" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W11" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W11" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-11</v>
       </c>
       <c r="X11" s="43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y11" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z11" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA11" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to an environment equipped to fulfill ward functions.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="40">
         <v>12</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E12" s="50" t="s">
-        <v>135</v>
-      </c>
       <c r="F12" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G12" s="41" t="s">
         <v>1</v>
@@ -3084,12 +3141,12 @@
         <v>SUS.Laboratório</v>
       </c>
       <c r="P12" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q12" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="Q12" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="R12" s="44" t="s">
+      <c r="R12" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S12" s="42" t="str">
@@ -3105,44 +3162,44 @@
         <v>SUS.Laboratório</v>
       </c>
       <c r="V12" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W12" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W12" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-12</v>
       </c>
       <c r="X12" s="43" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z12" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA12" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to an environment equipped to perform laboratory functions.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="40">
         <v>13</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D13" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="50" t="s">
-        <v>135</v>
-      </c>
       <c r="F13" s="51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G13" s="41" t="s">
         <v>1</v>
@@ -3176,12 +3233,12 @@
         <v>SUS.Piscina</v>
       </c>
       <c r="P13" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q13" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="Q13" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="R13" s="44" t="s">
+      <c r="R13" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S13" s="42" t="str">
@@ -3197,44 +3254,44 @@
         <v>SUS.Piscina</v>
       </c>
       <c r="V13" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W13" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W13" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-13</v>
       </c>
       <c r="X13" s="43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y13" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z13" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA13" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a closed or open environment for medical treatment pools.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="40">
         <v>14</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D14" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E14" s="50" t="s">
-        <v>135</v>
-      </c>
       <c r="F14" s="51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G14" s="41" t="s">
         <v>1</v>
@@ -3268,12 +3325,12 @@
         <v>SUS.Posto</v>
       </c>
       <c r="P14" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q14" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="Q14" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="R14" s="44" t="s">
+      <c r="R14" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S14" s="42" t="str">
@@ -3289,44 +3346,44 @@
         <v>SUS.Posto</v>
       </c>
       <c r="V14" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W14" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W14" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-14</v>
       </c>
       <c r="X14" s="43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y14" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z14" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA14" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a nursing station associated with an infirmary.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="40">
         <v>15</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E15" s="50" t="s">
-        <v>135</v>
-      </c>
       <c r="F15" s="51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G15" s="41" t="s">
         <v>1</v>
@@ -3360,12 +3417,12 @@
         <v>SUS.Quarto</v>
       </c>
       <c r="P15" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q15" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="Q15" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="R15" s="44" t="s">
+      <c r="R15" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S15" s="42" t="str">
@@ -3381,44 +3438,44 @@
         <v>SUS.Quarto</v>
       </c>
       <c r="V15" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W15" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W15" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-15</v>
       </c>
       <c r="X15" s="43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y15" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA15" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a hospitalization room.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="40">
         <v>16</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D16" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E16" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E16" s="50" t="s">
-        <v>135</v>
-      </c>
       <c r="F16" s="52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G16" s="41" t="s">
         <v>1</v>
@@ -3452,12 +3509,12 @@
         <v>SUS.Sala</v>
       </c>
       <c r="P16" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q16" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="Q16" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="R16" s="44" t="s">
+      <c r="R16" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="42" t="str">
@@ -3473,44 +3530,44 @@
         <v>SUS.Sala</v>
       </c>
       <c r="V16" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W16" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W16" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-16</v>
       </c>
       <c r="X16" s="43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Y16" s="43" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z16" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA16" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a room to function as administrative or technical service.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="40">
         <v>17</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G17" s="41" t="s">
         <v>1</v>
@@ -3544,12 +3601,12 @@
         <v>SUS.Zoneamento</v>
       </c>
       <c r="P17" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q17" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="Q17" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="R17" s="44" t="s">
+      <c r="R17" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S17" s="42" t="str">
@@ -3565,44 +3622,44 @@
         <v>SUS.Zoneamento</v>
       </c>
       <c r="V17" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W17" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W17" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-17</v>
       </c>
       <c r="X17" s="43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="Y17" s="43" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Z17" s="44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA17" s="43" t="str">
         <f t="shared" si="8"/>
         <v>It refers to a defined zoning.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="40">
         <v>18</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>1</v>
@@ -3636,12 +3693,12 @@
         <v>SUS.Unidade.Funcional</v>
       </c>
       <c r="P18" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q18" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="Q18" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="R18" s="44" t="s">
+      <c r="R18" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S18" s="42" t="str">
@@ -3657,10 +3714,10 @@
         <v>SUS.Unidade.Funcional</v>
       </c>
       <c r="V18" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W18" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W18" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-18</v>
       </c>
       <c r="X18" s="43" t="s">
@@ -3670,31 +3727,31 @@
         <v>1</v>
       </c>
       <c r="Z18" s="44" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AA18" s="43" t="str">
         <f t="shared" si="8"/>
         <v>They are the functional units of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="40">
         <v>19</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G19" s="41" t="s">
         <v>1</v>
@@ -3728,12 +3785,12 @@
         <v>SUS.Setor</v>
       </c>
       <c r="P19" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q19" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="Q19" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="R19" s="44" t="s">
+      <c r="R19" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S19" s="42" t="str">
@@ -3749,10 +3806,10 @@
         <v>SUS.Setor</v>
       </c>
       <c r="V19" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W19" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W19" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-19</v>
       </c>
       <c r="X19" s="43" t="s">
@@ -3762,31 +3819,31 @@
         <v>1</v>
       </c>
       <c r="Z19" s="44" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AA19" s="43" t="str">
         <f t="shared" si="8"/>
         <v>They are the Sectors of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="40">
         <v>20</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G20" s="41" t="s">
         <v>1</v>
@@ -3820,12 +3877,12 @@
         <v>SUS.Robot</v>
       </c>
       <c r="P20" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q20" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="Q20" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="R20" s="44" t="s">
+      <c r="R20" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S20" s="42" t="str">
@@ -3841,44 +3898,44 @@
         <v>SUS.Robot</v>
       </c>
       <c r="V20" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W20" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W20" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-20</v>
       </c>
       <c r="X20" s="43" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="Y20" s="43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="Z20" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA20" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="40">
         <v>21</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G21" s="41" t="s">
         <v>1</v>
@@ -3912,12 +3969,12 @@
         <v>SUS.Equipamento</v>
       </c>
       <c r="P21" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q21" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="Q21" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="R21" s="44" t="s">
+      <c r="R21" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S21" s="42" t="str">
@@ -3933,44 +3990,44 @@
         <v>SUS.Equipamento</v>
       </c>
       <c r="V21" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W21" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W21" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-21</v>
       </c>
       <c r="X21" s="43" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="Y21" s="43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="Z21" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA21" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="40">
         <v>22</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G22" s="41" t="s">
         <v>1</v>
@@ -4004,12 +4061,12 @@
         <v>SUS.Dispositivo</v>
       </c>
       <c r="P22" s="42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q22" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="R22" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="R22" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S22" s="42" t="str">
@@ -4025,44 +4082,44 @@
         <v>SUS.Dispositivo</v>
       </c>
       <c r="V22" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W22" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W22" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-22</v>
       </c>
       <c r="X22" s="43" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="Y22" s="43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="Z22" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA22" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="40">
         <v>23</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G23" s="41" t="s">
         <v>1</v>
@@ -4096,12 +4153,12 @@
         <v>SUS.Instrumento</v>
       </c>
       <c r="P23" s="42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q23" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="R23" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="R23" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S23" s="42" t="str">
@@ -4117,44 +4174,44 @@
         <v>SUS.Instrumento</v>
       </c>
       <c r="V23" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W23" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W23" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-23</v>
       </c>
       <c r="X23" s="43" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="Y23" s="43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="Z23" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA23" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>24</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G24" s="41" t="s">
         <v>1</v>
@@ -4188,12 +4245,12 @@
         <v>SUS.Mobília.de.Saúde</v>
       </c>
       <c r="P24" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q24" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="Q24" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="R24" s="44" t="s">
+      <c r="R24" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S24" s="42" t="str">
@@ -4209,44 +4266,44 @@
         <v>SUS.Mobília.de.Saúde</v>
       </c>
       <c r="V24" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W24" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W24" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-24</v>
       </c>
       <c r="X24" s="43" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Y24" s="43" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="Z24" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA24" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>25</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F25" s="53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="41" t="s">
         <v>1</v>
@@ -4280,12 +4337,12 @@
         <v>SUS.Mobília</v>
       </c>
       <c r="P25" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q25" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="Q25" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="R25" s="44" t="s">
+      <c r="R25" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S25" s="42" t="str">
@@ -4301,44 +4358,44 @@
         <v>SUS.Mobília</v>
       </c>
       <c r="V25" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W25" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W25" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-25</v>
       </c>
       <c r="X25" s="43" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Y25" s="43" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="Z25" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA25" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>26</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E26" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" s="53" t="s">
         <v>163</v>
-      </c>
-      <c r="F26" s="53" t="s">
-        <v>164</v>
       </c>
       <c r="G26" s="41" t="s">
         <v>1</v>
@@ -4372,12 +4429,12 @@
         <v>SUS.Roupa</v>
       </c>
       <c r="P26" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q26" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="Q26" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="R26" s="44" t="s">
+      <c r="R26" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S26" s="42" t="str">
@@ -4393,44 +4450,44 @@
         <v>SUS.Roupa</v>
       </c>
       <c r="V26" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W26" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W26" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-26</v>
       </c>
       <c r="X26" s="43" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Y26" s="43" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="Z26" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA26" s="43" t="str">
         <f t="shared" si="8"/>
         <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>27</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F27" s="53" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G27" s="41" t="s">
         <v>1</v>
@@ -4464,12 +4521,12 @@
         <v>SUS.Alimentação</v>
       </c>
       <c r="P27" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q27" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="Q27" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="R27" s="44" t="s">
+      <c r="R27" s="45" t="s">
         <v>1</v>
       </c>
       <c r="S27" s="42" t="str">
@@ -4485,20 +4542,20 @@
         <v>SUS.Alimentação</v>
       </c>
       <c r="V27" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="W27" s="55" t="str">
-        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="W27" s="56" t="str">
+        <f t="shared" si="3"/>
         <v>Key-SUS-27</v>
       </c>
       <c r="X27" s="43" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Y27" s="43" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="Z27" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA27" s="43" t="str">
         <f t="shared" si="8"/>
@@ -4507,40 +4564,50 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A27">
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+  <conditionalFormatting sqref="A7:A27">
+    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:F27 L7:Q27">
-    <cfRule type="cellIs" dxfId="22" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F7:F23">
-    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V27 Z7:XFD7 S7:U27 X8:XFD17 Z18:XFD19 X20:XFD27">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+  <conditionalFormatting sqref="Z7:XFD7 S7:V27 X8:XFD17 Z18:XFD19 X20:XFD27">
+    <cfRule type="cellIs" dxfId="16" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA1">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B6 B7:B27">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4556,19 +4623,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.3828125" style="5"/>
+    <col min="22" max="16384" width="5.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="30" t="s">
         <v>13</v>
       </c>
@@ -4633,7 +4700,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -4701,7 +4768,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4717,25 +4784,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="16.3046875" customWidth="1"/>
-    <col min="3" max="3" width="19.3828125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9">
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -4748,7 +4815,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4760,26 +4827,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.61328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.3828125" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52.84375" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.69140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.84375" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.84375" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.53515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.765625" style="33" customWidth="1"/>
-    <col min="13" max="13" width="6.07421875" style="33" customWidth="1"/>
-    <col min="14" max="14" width="2.3828125" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -4826,7 +4893,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -4834,37 +4901,37 @@
         <v>78</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" s="37" t="s">
         <v>83</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F2" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I2" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="J2" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="J2" s="37" t="s">
-        <v>177</v>
-      </c>
       <c r="K2" s="32" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N2" s="37" t="s">
         <v>1</v>
@@ -4873,7 +4940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -4881,37 +4948,37 @@
         <v>79</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" s="37" t="s">
         <v>83</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F3" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G3" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="I3" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="H3" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="I3" s="32" t="s">
+      <c r="J3" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="J3" s="37" t="s">
-        <v>177</v>
-      </c>
       <c r="K3" s="32" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N3" s="37" t="s">
         <v>1</v>
@@ -4920,7 +4987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -4928,37 +4995,37 @@
         <v>80</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" s="37" t="s">
         <v>83</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F4" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I4" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="J4" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="J4" s="37" t="s">
-        <v>177</v>
-      </c>
       <c r="K4" s="32" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N4" s="37" t="s">
         <v>1</v>
@@ -4967,7 +5034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -4975,37 +5042,37 @@
         <v>81</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" s="37" t="s">
         <v>83</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F5" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I5" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="J5" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="J5" s="37" t="s">
-        <v>177</v>
-      </c>
       <c r="K5" s="32" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N5" s="37" t="s">
         <v>1</v>
@@ -5016,37 +5083,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA3B5E3-ED5E-4EF9-BBF6-D6A9F566D273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5276DA-8234-4966-A56F-0B864653396C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="243">
   <si>
     <t>Key</t>
   </si>
@@ -725,13 +725,97 @@
   </si>
   <si>
     <t>"[ - ]"</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>FonteSomaSUS</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -808,8 +892,22 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -942,6 +1040,12 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -991,10 +1095,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1151,74 +1256,36 @@
     <xf numFmtId="0" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -1750,15 +1817,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultRowHeight="10.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.3828125" customWidth="1"/>
+    <col min="2" max="2" width="48.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
@@ -1769,7 +1836,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
@@ -1780,7 +1847,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
@@ -1791,7 +1858,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -1802,7 +1869,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -1814,7 +1881,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -1826,7 +1893,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -1837,7 +1904,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
@@ -1848,7 +1915,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -1859,7 +1926,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -1870,7 +1937,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -1881,7 +1948,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -1892,7 +1959,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -1903,7 +1970,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -1914,7 +1981,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -1925,7 +1992,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -1936,7 +2003,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -1947,19 +2014,19 @@
         <v>169</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46216.346035648145</v>
+        <v>46233.491116319441</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
@@ -1970,7 +2037,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -1981,7 +2048,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>176</v>
       </c>
@@ -1992,7 +2059,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>173</v>
       </c>
@@ -2004,7 +2071,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>177</v>
       </c>
@@ -2016,7 +2083,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>72</v>
       </c>
@@ -2027,7 +2094,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
@@ -2038,7 +2105,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>166</v>
       </c>
@@ -2050,7 +2117,169 @@
         <v>171</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B28" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B29" s="60" t="s">
+        <v>220</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" s="61" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B33" s="57" t="s">
+        <v>228</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" s="57" t="s">
+        <v>230</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="61" t="s">
+        <v>232</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B36" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B37" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" s="62" t="s">
+        <v>238</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="58" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" s="63" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="58" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B40" s="63" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{5459870A-EA88-4D94-AECD-FB25ABC9E3FC}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{517B939F-01A7-4003-85A6-6C122E4F286F}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{79B7ECCC-039C-4CB2-AB5A-86C571F94E9E}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{601C1702-E1F4-4441-A0A3-884453A34A55}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{980343AA-51B7-4173-B919-F6A27B8E831B}"/>
+    <hyperlink ref="B40" r:id="rId6" xr:uid="{D7BD13C7-FFD2-43AB-8F15-8A3AFF357A49}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -2059,35 +2288,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.42578125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="1" customWidth="1"/>
-    <col min="7" max="11" width="6.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3828125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="5.53515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.15234375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.15234375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.15234375" style="1" customWidth="1"/>
+    <col min="7" max="11" width="6.84375" style="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" style="8" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" style="8" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" style="8" customWidth="1"/>
-    <col min="16" max="16" width="37.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="38.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="4.140625" style="54" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="8.85546875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.28515625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.85546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.42578125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="49.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.85546875" style="1"/>
+    <col min="13" max="13" width="11.15234375" style="8" customWidth="1"/>
+    <col min="14" max="14" width="9.3046875" style="8" customWidth="1"/>
+    <col min="15" max="15" width="10.84375" style="8" customWidth="1"/>
+    <col min="16" max="16" width="37.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="38.69140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="4.15234375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.69140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.3828125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.84375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="8.84375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.3046875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.84375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9.3828125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="49.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -2154,7 +2383,7 @@
       <c r="V1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="55" t="s">
+      <c r="W1" s="54" t="s">
         <v>0</v>
       </c>
       <c r="X1" s="28" t="s">
@@ -2170,7 +2399,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="40">
         <v>2</v>
       </c>
@@ -2244,7 +2473,7 @@
       <c r="V2" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="W2" s="56" t="str">
+      <c r="W2" s="55" t="str">
         <f t="shared" ref="W2:W27" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
@@ -2262,7 +2491,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="40">
         <v>3</v>
       </c>
@@ -2336,7 +2565,7 @@
       <c r="V3" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="W3" s="56" t="str">
+      <c r="W3" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-3</v>
       </c>
@@ -2354,7 +2583,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="40">
         <v>4</v>
       </c>
@@ -2428,7 +2657,7 @@
       <c r="V4" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="W4" s="56" t="str">
+      <c r="W4" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-4</v>
       </c>
@@ -2446,7 +2675,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="40">
         <v>5</v>
       </c>
@@ -2520,7 +2749,7 @@
       <c r="V5" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="W5" s="56" t="str">
+      <c r="W5" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-5</v>
       </c>
@@ -2538,7 +2767,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="40">
         <v>6</v>
       </c>
@@ -2612,7 +2841,7 @@
       <c r="V6" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="W6" s="56" t="str">
+      <c r="W6" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-6</v>
       </c>
@@ -2630,7 +2859,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="40">
         <v>7</v>
       </c>
@@ -2704,7 +2933,7 @@
       <c r="V7" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W7" s="56" t="str">
+      <c r="W7" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-7</v>
       </c>
@@ -2722,7 +2951,7 @@
         <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="40">
         <v>8</v>
       </c>
@@ -2796,7 +3025,7 @@
       <c r="V8" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W8" s="56" t="str">
+      <c r="W8" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-8</v>
       </c>
@@ -2814,7 +3043,7 @@
         <v>It refers to an environment that is not totally cloistered.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="40">
         <v>9</v>
       </c>
@@ -2888,7 +3117,7 @@
       <c r="V9" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W9" s="56" t="str">
+      <c r="W9" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-9</v>
       </c>
@@ -2906,7 +3135,7 @@
         <v>It refers to a closed and small environment, usually to serve patients.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="40">
         <v>10</v>
       </c>
@@ -2980,7 +3209,7 @@
       <c r="V10" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W10" s="56" t="str">
+      <c r="W10" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-10</v>
       </c>
@@ -2998,7 +3227,7 @@
         <v>It refers to a doctor's office-type environment.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="40">
         <v>11</v>
       </c>
@@ -3072,7 +3301,7 @@
       <c r="V11" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W11" s="56" t="str">
+      <c r="W11" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-11</v>
       </c>
@@ -3090,7 +3319,7 @@
         <v>It refers to an environment equipped to fulfill ward functions.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="40">
         <v>12</v>
       </c>
@@ -3164,7 +3393,7 @@
       <c r="V12" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W12" s="56" t="str">
+      <c r="W12" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-12</v>
       </c>
@@ -3182,7 +3411,7 @@
         <v>It refers to an environment equipped to perform laboratory functions.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="40">
         <v>13</v>
       </c>
@@ -3256,7 +3485,7 @@
       <c r="V13" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W13" s="56" t="str">
+      <c r="W13" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-13</v>
       </c>
@@ -3274,7 +3503,7 @@
         <v>It refers to a closed or open environment for medical treatment pools.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="40">
         <v>14</v>
       </c>
@@ -3348,7 +3577,7 @@
       <c r="V14" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W14" s="56" t="str">
+      <c r="W14" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-14</v>
       </c>
@@ -3366,7 +3595,7 @@
         <v>It refers to a nursing station associated with an infirmary.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="40">
         <v>15</v>
       </c>
@@ -3440,7 +3669,7 @@
       <c r="V15" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W15" s="56" t="str">
+      <c r="W15" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-15</v>
       </c>
@@ -3458,7 +3687,7 @@
         <v>It refers to a hospitalization room.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="40">
         <v>16</v>
       </c>
@@ -3532,7 +3761,7 @@
       <c r="V16" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W16" s="56" t="str">
+      <c r="W16" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-16</v>
       </c>
@@ -3550,7 +3779,7 @@
         <v>It refers to a room to function as administrative or technical service.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="40">
         <v>17</v>
       </c>
@@ -3624,7 +3853,7 @@
       <c r="V17" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W17" s="56" t="str">
+      <c r="W17" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-17</v>
       </c>
@@ -3642,7 +3871,7 @@
         <v>It refers to a defined zoning.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="40">
         <v>18</v>
       </c>
@@ -3716,7 +3945,7 @@
       <c r="V18" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W18" s="56" t="str">
+      <c r="W18" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-18</v>
       </c>
@@ -3734,7 +3963,7 @@
         <v>They are the functional units of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="40">
         <v>19</v>
       </c>
@@ -3808,7 +4037,7 @@
       <c r="V19" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W19" s="56" t="str">
+      <c r="W19" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-19</v>
       </c>
@@ -3826,7 +4055,7 @@
         <v>They are the Sectors of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="40">
         <v>20</v>
       </c>
@@ -3900,7 +4129,7 @@
       <c r="V20" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W20" s="56" t="str">
+      <c r="W20" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-20</v>
       </c>
@@ -3918,7 +4147,7 @@
         <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="40">
         <v>21</v>
       </c>
@@ -3992,7 +4221,7 @@
       <c r="V21" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W21" s="56" t="str">
+      <c r="W21" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-21</v>
       </c>
@@ -4010,7 +4239,7 @@
         <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40">
         <v>22</v>
       </c>
@@ -4084,7 +4313,7 @@
       <c r="V22" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W22" s="56" t="str">
+      <c r="W22" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-22</v>
       </c>
@@ -4102,7 +4331,7 @@
         <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="40">
         <v>23</v>
       </c>
@@ -4176,7 +4405,7 @@
       <c r="V23" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W23" s="56" t="str">
+      <c r="W23" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-23</v>
       </c>
@@ -4194,7 +4423,7 @@
         <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="40">
         <v>24</v>
       </c>
@@ -4268,7 +4497,7 @@
       <c r="V24" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W24" s="56" t="str">
+      <c r="W24" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-24</v>
       </c>
@@ -4286,7 +4515,7 @@
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="40">
         <v>25</v>
       </c>
@@ -4360,7 +4589,7 @@
       <c r="V25" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W25" s="56" t="str">
+      <c r="W25" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-25</v>
       </c>
@@ -4378,7 +4607,7 @@
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="40">
         <v>26</v>
       </c>
@@ -4452,7 +4681,7 @@
       <c r="V26" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W26" s="56" t="str">
+      <c r="W26" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-26</v>
       </c>
@@ -4470,7 +4699,7 @@
         <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="40">
         <v>27</v>
       </c>
@@ -4544,7 +4773,7 @@
       <c r="V27" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="W27" s="56" t="str">
+      <c r="W27" s="55" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-27</v>
       </c>
@@ -4564,50 +4793,40 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A7:A27">
-    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:B27">
+    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:F27 L7:Q27">
-    <cfRule type="cellIs" dxfId="28" priority="22" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F23">
-    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:XFD7 S7:V27 X8:XFD17 Z18:XFD19 X20:XFD27">
-    <cfRule type="cellIs" dxfId="16" priority="19" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B27">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+  <conditionalFormatting sqref="F7:F23">
+    <cfRule type="duplicateValues" dxfId="17" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F27">
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:XFD7 S7:V27 X8:XFD17 Z18:XFD19 X20:XFD27">
+    <cfRule type="cellIs" dxfId="10" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA6">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4623,19 +4842,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.42578125" style="5"/>
+    <col min="22" max="16384" width="5.3828125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="30" t="s">
         <v>13</v>
       </c>
@@ -4700,7 +4919,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -4768,7 +4987,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4784,14 +5003,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -4802,7 +5021,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -4815,7 +5034,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4827,26 +5046,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.84375" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.69140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3828125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.69140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.53515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.84375" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -4893,7 +5112,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -4940,7 +5159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -4987,7 +5206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -5034,7 +5253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -5083,37 +5302,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5276DA-8234-4966-A56F-0B864653396C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4593777-0C78-4B34-B3E4-06217EA5B3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="242">
   <si>
     <t>Key</t>
   </si>
@@ -712,15 +712,9 @@
     <t>"Volume 2 - Internação e Apoio ao Diagnóstico e à Terapia (Reabilitação)"</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
-    <t>Arquitetura</t>
-  </si>
-  <si>
     <t>[ 5I ]</t>
   </si>
   <si>
@@ -809,6 +803,9 @@
   </si>
   <si>
     <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
   </si>
 </sst>
 </file>
@@ -1291,6 +1288,14 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0"/>
       </font>
     </dxf>
@@ -1483,14 +1488,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2020,7 +2017,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46233.491116319441</v>
+        <v>46243.446685648145</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>169</v>
@@ -2119,10 +2116,10 @@
     </row>
     <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>169</v>
@@ -2130,10 +2127,10 @@
     </row>
     <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B28" s="60" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>169</v>
@@ -2141,10 +2138,10 @@
     </row>
     <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B29" s="60" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>169</v>
@@ -2152,10 +2149,10 @@
     </row>
     <row r="30" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B30" s="61" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>169</v>
@@ -2163,10 +2160,10 @@
     </row>
     <row r="31" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B31" s="61" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>169</v>
@@ -2174,10 +2171,10 @@
     </row>
     <row r="32" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B32" s="61" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>169</v>
@@ -2185,10 +2182,10 @@
     </row>
     <row r="33" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B33" s="57" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>169</v>
@@ -2196,10 +2193,10 @@
     </row>
     <row r="34" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B34" s="57" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>169</v>
@@ -2207,10 +2204,10 @@
     </row>
     <row r="35" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B35" s="61" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>169</v>
@@ -2218,10 +2215,10 @@
     </row>
     <row r="36" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B36" s="57" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>169</v>
@@ -2229,10 +2226,10 @@
     </row>
     <row r="37" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B37" s="61" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C37" s="36" t="s">
         <v>169</v>
@@ -2240,10 +2237,10 @@
     </row>
     <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B38" s="62" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C38" s="36" t="s">
         <v>169</v>
@@ -2251,10 +2248,10 @@
     </row>
     <row r="39" spans="1:3" s="58" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B39" s="63" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C39" s="36" t="s">
         <v>169</v>
@@ -2262,10 +2259,10 @@
     </row>
     <row r="40" spans="1:3" s="58" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B40" s="63" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C40" s="36" t="s">
         <v>169</v>
@@ -2308,7 +2305,7 @@
     <col min="20" max="20" width="8.3828125" style="1" customWidth="1"/>
     <col min="21" max="21" width="9.84375" style="1" customWidth="1"/>
     <col min="22" max="22" width="8.84375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.53515625" style="1" customWidth="1"/>
     <col min="24" max="24" width="21.3046875" style="1" customWidth="1"/>
     <col min="25" max="25" width="8.84375" style="1" customWidth="1"/>
     <col min="26" max="26" width="9.3828125" style="1" customWidth="1"/>
@@ -2404,7 +2401,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C2" s="46" t="s">
         <v>193</v>
@@ -2413,7 +2410,7 @@
         <v>129</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>130</v>
@@ -2471,7 +2468,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="43" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="W2" s="55" t="str">
         <f t="shared" ref="W2:W27" si="3">CONCATENATE("Key-SUS-",A2)</f>
@@ -2484,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AA2" s="43" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -2496,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C3" s="46" t="s">
         <v>193</v>
@@ -2505,7 +2502,7 @@
         <v>129</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F3" s="47" t="s">
         <v>194</v>
@@ -2563,7 +2560,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="43" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="W3" s="55" t="str">
         <f t="shared" si="3"/>
@@ -2588,7 +2585,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C4" s="46" t="s">
         <v>193</v>
@@ -2597,7 +2594,7 @@
         <v>129</v>
       </c>
       <c r="E4" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F4" s="47" t="s">
         <v>196</v>
@@ -2655,7 +2652,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="43" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="W4" s="55" t="str">
         <f t="shared" si="3"/>
@@ -2680,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C5" s="46" t="s">
         <v>193</v>
@@ -2689,7 +2686,7 @@
         <v>129</v>
       </c>
       <c r="E5" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F5" s="47" t="s">
         <v>198</v>
@@ -2747,7 +2744,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="43" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="W5" s="55" t="str">
         <f t="shared" si="3"/>
@@ -2772,7 +2769,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C6" s="46" t="s">
         <v>193</v>
@@ -2781,7 +2778,7 @@
         <v>129</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F6" s="47" t="s">
         <v>200</v>
@@ -2839,7 +2836,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="43" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="W6" s="55" t="str">
         <f t="shared" si="3"/>
@@ -2864,7 +2861,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C7" s="47" t="s">
         <v>93</v>
@@ -2956,7 +2953,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C8" s="47" t="s">
         <v>93</v>
@@ -3048,7 +3045,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C9" s="47" t="s">
         <v>93</v>
@@ -3140,7 +3137,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C10" s="47" t="s">
         <v>93</v>
@@ -3232,7 +3229,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C11" s="47" t="s">
         <v>93</v>
@@ -3324,7 +3321,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C12" s="47" t="s">
         <v>93</v>
@@ -3416,7 +3413,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C13" s="47" t="s">
         <v>93</v>
@@ -3508,7 +3505,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C14" s="47" t="s">
         <v>93</v>
@@ -3600,7 +3597,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C15" s="47" t="s">
         <v>93</v>
@@ -3692,7 +3689,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C16" s="47" t="s">
         <v>93</v>
@@ -3784,7 +3781,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C17" s="47" t="s">
         <v>93</v>
@@ -3876,7 +3873,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C18" s="47" t="s">
         <v>93</v>
@@ -3968,7 +3965,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C19" s="47" t="s">
         <v>93</v>
@@ -4060,7 +4057,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C20" s="47" t="s">
         <v>93</v>
@@ -4152,7 +4149,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C21" s="47" t="s">
         <v>93</v>
@@ -4244,7 +4241,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C22" s="47" t="s">
         <v>93</v>
@@ -4336,7 +4333,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C23" s="47" t="s">
         <v>93</v>
@@ -4428,7 +4425,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C24" s="47" t="s">
         <v>93</v>
@@ -4520,7 +4517,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C25" s="47" t="s">
         <v>93</v>
@@ -4612,7 +4609,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C26" s="47" t="s">
         <v>93</v>
@@ -4704,7 +4701,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C27" s="47" t="s">
         <v>93</v>
@@ -4794,39 +4791,39 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B27">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:F27 L7:Q27">
-    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F23">
-    <cfRule type="duplicateValues" dxfId="17" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:XFD7 S7:V27 X8:XFD17 Z18:XFD19 X20:XFD27">
-    <cfRule type="cellIs" dxfId="10" priority="19" operator="equal">
+  <conditionalFormatting sqref="Z7:XFD7 S7:V27 X8:XFD17 Z18:XFD19 X20:XFD27 V2:V6">
+    <cfRule type="cellIs" dxfId="11" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA6">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4987,7 +4984,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5034,7 +5031,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5138,13 +5135,13 @@
         <v>174</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J2" s="37" t="s">
         <v>175</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L2" s="37" t="s">
         <v>204</v>
@@ -5185,13 +5182,13 @@
         <v>174</v>
       </c>
       <c r="I3" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J3" s="37" t="s">
         <v>175</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L3" s="37" t="s">
         <v>204</v>
@@ -5232,13 +5229,13 @@
         <v>174</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J4" s="37" t="s">
         <v>175</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L4" s="37" t="s">
         <v>204</v>
@@ -5279,13 +5276,13 @@
         <v>174</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J5" s="37" t="s">
         <v>175</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L5" s="37" t="s">
         <v>204</v>
@@ -5302,37 +5299,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4593777-0C78-4B34-B3E4-06217EA5B3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AF3B41-7E57-4BF4-A42E-3C53ED0CB46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="228">
   <si>
     <t>Key</t>
   </si>
@@ -361,9 +361,6 @@
     <t>SUS.Mobília</t>
   </si>
   <si>
-    <t>SUS</t>
-  </si>
-  <si>
     <t>Classe</t>
   </si>
   <si>
@@ -469,15 +466,6 @@
     <t>Mobiliario médico utilizado en hospitales del Sistema Único de Salud de Brasil.</t>
   </si>
   <si>
-    <t>Informação</t>
-  </si>
-  <si>
-    <t>Contêiner</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
     <t>SUS.Caderno</t>
   </si>
   <si>
@@ -616,78 +604,33 @@
     <t>Alert</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
     <t>[ 5I.10.54.12.16 ]</t>
   </si>
   <si>
-    <t>[ OST_Rooms , OST_MEPSpaces ]</t>
-  </si>
-  <si>
     <t>[ IfcSpace ]</t>
   </si>
   <si>
     <t>[ 4A.43.04 ]</t>
   </si>
   <si>
-    <t>[ OST_Areas ]</t>
-  </si>
-  <si>
-    <t>[ OST_MEPZone ]</t>
-  </si>
-  <si>
     <t>[ IfcZone ]</t>
   </si>
   <si>
     <t>[ 4U.74 ]</t>
   </si>
   <si>
-    <t>[ OST_MedicalEquipment ]</t>
-  </si>
-  <si>
     <t>[ IfcMedicalDevice ]</t>
   </si>
   <si>
     <t>[ 2C.74 ]</t>
   </si>
   <si>
-    <t>[ OST_MedicalEquipment , OST_NurseCallDevices ]</t>
-  </si>
-  <si>
     <t>[ OST_Furniture ]</t>
   </si>
   <si>
     <t>[ IfcFurniture ]</t>
   </si>
   <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>Requisito.Espacial</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Mobiliário</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Equipamento</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Sistemas</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>Hospitalar</t>
   </si>
   <si>
@@ -712,12 +655,6 @@
     <t>"Volume 2 - Internação e Apoio ao Diagnóstico e à Terapia (Reabilitação)"</t>
   </si>
   <si>
-    <t>Contêineres</t>
-  </si>
-  <si>
-    <t>[ 5I ]</t>
-  </si>
-  <si>
     <t>"[ - ]"</t>
   </si>
   <si>
@@ -806,6 +743,27 @@
   </si>
   <si>
     <t>Conceitos</t>
+  </si>
+  <si>
+    <t>SUS.Informação</t>
+  </si>
+  <si>
+    <t>[ OST_Areas : OST_Rooms : OST_MEPSpaces ]</t>
+  </si>
+  <si>
+    <t>[ OST_Areas : OST_Rooms : OST_MEPSpaces : OST_MEPZone ]</t>
+  </si>
+  <si>
+    <t>[ IfcZone : IfcSpace ]</t>
+  </si>
+  <si>
+    <t>[ OST_MedicalEquipment : OST_NurseCallDevices ]</t>
+  </si>
+  <si>
+    <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
+  </si>
+  <si>
+    <t>[ IfcAnnotation ]</t>
   </si>
 </sst>
 </file>
@@ -1027,20 +985,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor theme="0"/>
+        <fgColor rgb="FFFFDE75"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFDE75"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1096,7 +1054,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1224,33 +1182,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1262,7 +1193,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1276,13 +1207,69 @@
     </xf>
     <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1381,13 +1368,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1461,33 +1446,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1815,14 +1778,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="10.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.3828125" customWidth="1"/>
-    <col min="2" max="2" width="48.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
@@ -1830,21 +1793,21 @@
         <v>48</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
@@ -1852,10 +1815,10 @@
         <v>77</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -1863,10 +1826,10 @@
         <v>25</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -1875,10 +1838,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -1887,10 +1850,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -1898,21 +1861,21 @@
         <v>55</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -1920,10 +1883,10 @@
         <v>58</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -1931,10 +1894,10 @@
         <v>60</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -1942,10 +1905,10 @@
         <v>60</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -1953,10 +1916,10 @@
         <v>60</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -1964,10 +1927,10 @@
         <v>82</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -1975,10 +1938,10 @@
         <v>60</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -1986,10 +1949,10 @@
         <v>60</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -1997,10 +1960,10 @@
         <v>60</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -2008,22 +1971,22 @@
         <v>68</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46243.446685648145</v>
+        <v>46244.499835069444</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
@@ -2031,10 +1994,10 @@
         <v>60</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2042,56 +2005,56 @@
         <v>60</v>
       </c>
       <c r="C20" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="14" t="s">
-        <v>173</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>_xlfn.TRANSLATE(B21,"pt","es")</f>
         <v>Cuaderno SomaSUS preparado por el Sistema Unificado de Salud de Brasil</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Cuaderno SomaSUS prepared by the Unified Health System of Brazil</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
@@ -2099,173 +2062,173 @@
         <v>74</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize the SomaSUS Notebook prepared by the Unified Health System of Brazil.</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B36" s="48" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="B27" s="59" t="s">
+      <c r="C37" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="14" t="s">
+      <c r="B38" s="53" t="s">
         <v>215</v>
       </c>
-      <c r="B28" s="60" t="s">
+      <c r="C38" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="14" t="s">
+      <c r="B39" s="54" t="s">
         <v>217</v>
       </c>
-      <c r="B29" s="60" t="s">
+      <c r="C39" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="s">
+      <c r="B40" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="B31" s="61" t="s">
-        <v>222</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="B32" s="61" t="s">
-        <v>224</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="B33" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B34" s="57" t="s">
-        <v>228</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="B35" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="B36" s="57" t="s">
-        <v>232</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B37" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="B38" s="62" t="s">
-        <v>236</v>
-      </c>
-      <c r="C38" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="58" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="B39" s="63" t="s">
-        <v>238</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="58" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="B40" s="63" t="s">
-        <v>240</v>
-      </c>
       <c r="C40" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2284,36 +2247,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AA22"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3828125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="5.53515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.15234375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.15234375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.15234375" style="1" customWidth="1"/>
-    <col min="7" max="11" width="6.84375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.15234375" style="8" customWidth="1"/>
-    <col min="14" max="14" width="9.3046875" style="8" customWidth="1"/>
-    <col min="15" max="15" width="10.84375" style="8" customWidth="1"/>
-    <col min="16" max="16" width="37.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="38.69140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="4.15234375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.69140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.3828125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.84375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="8.84375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="7.53515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="21.3046875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.84375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.3828125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="49.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.84375" style="1"/>
+    <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="47.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -2380,40 +2343,40 @@
       <c r="V1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="54" t="s">
+      <c r="W1" s="45" t="s">
         <v>0</v>
       </c>
       <c r="X1" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y1" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="Y1" s="28" t="s">
+      <c r="Z1" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="Z1" s="28" t="s">
-        <v>100</v>
-      </c>
       <c r="AA1" s="39" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="40">
         <v>2</v>
       </c>
-      <c r="B2" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>130</v>
+      <c r="B2" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="58" t="s">
+        <v>95</v>
       </c>
       <c r="G2" s="41" t="s">
         <v>1</v>
@@ -2431,81 +2394,81 @@
         <v>1</v>
       </c>
       <c r="L2" s="42" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
+        <f t="shared" ref="L2:N2" si="0">CONCATENATE("", C2)</f>
+        <v>SomaSUS</v>
       </c>
       <c r="M2" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>Informação</v>
+        <v>SUS.Caderno</v>
       </c>
       <c r="N2" s="42" t="str">
-        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Contêineres</v>
+        <f t="shared" si="0"/>
+        <v>SUS.Informação</v>
       </c>
       <c r="O2" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="P2" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q2" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="R2" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="45" t="str">
-        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Gestão</v>
-      </c>
-      <c r="T2" s="45" t="str">
+        <f t="shared" ref="O2" si="1">F2</f>
+        <v>SUS.Volume</v>
+      </c>
+      <c r="P2" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="R2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="42" t="str">
+        <f t="shared" ref="S2:U2" si="2">SUBSTITUTE(D2, "_", " ")</f>
+        <v>SUS.Caderno</v>
+      </c>
+      <c r="T2" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U2" s="45" t="str">
+        <v>SUS.Informação</v>
+      </c>
+      <c r="U2" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <v>SUS.Volume</v>
       </c>
       <c r="V2" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W2" s="55" t="str">
-        <f t="shared" ref="W2:W27" si="3">CONCATENATE("Key-SUS-",A2)</f>
+        <v>183</v>
+      </c>
+      <c r="W2" s="46" t="str">
+        <f t="shared" ref="W2" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
-      <c r="X2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="43" t="s">
-        <v>1</v>
+      <c r="X2" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y2" s="64" t="s">
+        <v>227</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="AA2" s="43" t="str">
-        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="AA2" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="40">
         <v>3</v>
       </c>
-      <c r="B3" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" s="46" t="s">
+      <c r="B3" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="F3" s="47" t="s">
-        <v>194</v>
+      <c r="E3" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>86</v>
       </c>
       <c r="G3" s="41" t="s">
         <v>1</v>
@@ -2523,81 +2486,81 @@
         <v>1</v>
       </c>
       <c r="L3" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <f t="shared" ref="L2:N21" si="5">CONCATENATE("", C3)</f>
+        <v>SomaSUS</v>
       </c>
       <c r="M3" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
+        <f t="shared" si="5"/>
+        <v>SUS.Ocupação</v>
       </c>
       <c r="N3" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
+        <f t="shared" si="5"/>
+        <v>SUS.Ambientes</v>
       </c>
       <c r="O3" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Espacial</v>
-      </c>
-      <c r="P3" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q3" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="R3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T3" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U3" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" ref="O2:O22" si="6">F3</f>
+        <v>SUS.Area</v>
+      </c>
+      <c r="P3" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q3" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="R3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="42" t="str">
+        <f t="shared" ref="S2:U21" si="7">SUBSTITUTE(D3, "_", " ")</f>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="T3" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="U3" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Area</v>
       </c>
       <c r="V3" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W3" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W3" s="46" t="str">
+        <f t="shared" ref="W2:W22" si="8">CONCATENATE("Key-SUS-",A3)</f>
         <v>Key-SUS-3</v>
       </c>
       <c r="X3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="45" t="s">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="Y3" s="43" t="s">
+        <v>175</v>
       </c>
       <c r="Z3" s="44" t="s">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="AA3" s="43" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="AA2:AA22" si="9">_xlfn.TRANSLATE(P3,"pt","en")</f>
+        <v>It refers to an environment that is not totally cloistered.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="40">
         <v>4</v>
       </c>
-      <c r="B4" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="D4" s="46" t="s">
+      <c r="B4" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>196</v>
+      <c r="E4" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>104</v>
       </c>
       <c r="G4" s="41" t="s">
         <v>1</v>
@@ -2615,81 +2578,81 @@
         <v>1</v>
       </c>
       <c r="L4" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <f t="shared" si="5"/>
+        <v>SomaSUS</v>
       </c>
       <c r="M4" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
+        <f t="shared" si="5"/>
+        <v>SUS.Ocupação</v>
       </c>
       <c r="N4" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
+        <f t="shared" si="5"/>
+        <v>SUS.Ambientes</v>
       </c>
       <c r="O4" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Mobiliário</v>
-      </c>
-      <c r="P4" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q4" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="R4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T4" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U4" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="6"/>
+        <v>SUS.Box</v>
+      </c>
+      <c r="P4" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q4" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="R4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="T4" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="U4" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Box</v>
       </c>
       <c r="V4" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W4" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W4" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-4</v>
       </c>
       <c r="X4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="45" t="s">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="Y4" s="43" t="s">
+        <v>175</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="AA4" s="43" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>It refers to a closed and small environment, usually to serve patients.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="40">
         <v>5</v>
       </c>
-      <c r="B5" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="46" t="s">
+      <c r="B5" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5" s="47" t="s">
-        <v>198</v>
+      <c r="E5" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="60" t="s">
+        <v>107</v>
       </c>
       <c r="G5" s="41" t="s">
         <v>1</v>
@@ -2707,81 +2670,81 @@
         <v>1</v>
       </c>
       <c r="L5" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <f t="shared" si="5"/>
+        <v>SomaSUS</v>
       </c>
       <c r="M5" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
+        <f t="shared" si="5"/>
+        <v>SUS.Ocupação</v>
       </c>
       <c r="N5" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
+        <f t="shared" si="5"/>
+        <v>SUS.Ambientes</v>
       </c>
       <c r="O5" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Equipamento</v>
-      </c>
-      <c r="P5" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q5" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="R5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T5" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U5" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="6"/>
+        <v>SUS.Consultório</v>
+      </c>
+      <c r="P5" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q5" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="R5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="T5" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="U5" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Consultório</v>
       </c>
       <c r="V5" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W5" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W5" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-5</v>
       </c>
       <c r="X5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="45" t="s">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="Y5" s="43" t="s">
+        <v>175</v>
       </c>
       <c r="Z5" s="44" t="s">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="AA5" s="43" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>It refers to a doctor's office-type environment.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="40">
         <v>6</v>
       </c>
-      <c r="B6" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" s="46" t="s">
+      <c r="B6" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>200</v>
+      <c r="E6" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>110</v>
       </c>
       <c r="G6" s="41" t="s">
         <v>1</v>
@@ -2799,81 +2762,81 @@
         <v>1</v>
       </c>
       <c r="L6" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
+        <f t="shared" si="5"/>
+        <v>SomaSUS</v>
       </c>
       <c r="M6" s="42" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
+        <f t="shared" si="5"/>
+        <v>SUS.Ocupação</v>
       </c>
       <c r="N6" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
+        <f t="shared" si="5"/>
+        <v>SUS.Ambientes</v>
       </c>
       <c r="O6" s="42" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Sistemas</v>
-      </c>
-      <c r="P6" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q6" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="R6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T6" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U6" s="45" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="6"/>
+        <v>SUS.Enfermaria</v>
+      </c>
+      <c r="P6" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q6" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="R6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="T6" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="U6" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>SUS.Enfermaria</v>
       </c>
       <c r="V6" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W6" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W6" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-6</v>
       </c>
       <c r="X6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="45" t="s">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="Y6" s="43" t="s">
+        <v>175</v>
       </c>
       <c r="Z6" s="44" t="s">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="AA6" s="43" t="str">
-        <f t="shared" si="4"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>It refers to an environment equipped to fulfill ward functions.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="40">
         <v>7</v>
       </c>
-      <c r="B7" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" s="48" t="s">
+      <c r="B7" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="49" t="s">
-        <v>96</v>
+      <c r="D7" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>112</v>
       </c>
       <c r="G7" s="41" t="s">
         <v>1</v>
@@ -2891,81 +2854,81 @@
         <v>1</v>
       </c>
       <c r="L7" s="42" t="str">
-        <f t="shared" ref="L7:N26" si="5">CONCATENATE("", C7)</f>
-        <v>SUS</v>
+        <f t="shared" si="5"/>
+        <v>SomaSUS</v>
       </c>
       <c r="M7" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Caderno</v>
+        <v>SUS.Ocupação</v>
       </c>
       <c r="N7" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
+        <v>SUS.Ambientes</v>
       </c>
       <c r="O7" s="42" t="str">
-        <f t="shared" ref="O7:O27" si="6">F7</f>
-        <v>SUS.Volume</v>
+        <f t="shared" si="6"/>
+        <v>SUS.Laboratório</v>
       </c>
       <c r="P7" s="42" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="Q7" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="R7" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="R7" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S7" s="42" t="str">
-        <f t="shared" ref="S7:U26" si="7">SUBSTITUTE(D7, "_", " ")</f>
-        <v>SUS.Caderno</v>
+        <f t="shared" si="7"/>
+        <v>SUS.Ocupação</v>
       </c>
       <c r="T7" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SomaSUS</v>
+        <v>SUS.Ambientes</v>
       </c>
       <c r="U7" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Volume</v>
+        <v>SUS.Laboratório</v>
       </c>
       <c r="V7" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W7" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W7" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-7</v>
       </c>
       <c r="X7" s="43" t="s">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="Y7" s="43" t="s">
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="Z7" s="44" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AA7" s="43" t="str">
-        <f t="shared" ref="AA7:AA27" si="8">_xlfn.TRANSLATE(P7,"pt","en")</f>
-        <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>It refers to an environment equipped to perform laboratory functions.</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="40">
         <v>8</v>
       </c>
-      <c r="B8" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>86</v>
+      <c r="B8" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="60" t="s">
+        <v>115</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>1</v>
@@ -2984,7 +2947,7 @@
       </c>
       <c r="L8" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M8" s="42" t="str">
         <f t="shared" si="5"/>
@@ -2996,15 +2959,15 @@
       </c>
       <c r="O8" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Area</v>
+        <v>SUS.Piscina</v>
       </c>
       <c r="P8" s="42" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="Q8" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="R8" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="R8" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="42" t="str">
@@ -3017,47 +2980,47 @@
       </c>
       <c r="U8" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Area</v>
+        <v>SUS.Piscina</v>
       </c>
       <c r="V8" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W8" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W8" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-8</v>
       </c>
       <c r="X8" s="43" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="Y8" s="43" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="Z8" s="44" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AA8" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to an environment that is not totally cloistered.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>It refers to a closed or open environment for medical treatment pools.</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="40">
         <v>9</v>
       </c>
-      <c r="B9" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>105</v>
+      <c r="B9" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>118</v>
       </c>
       <c r="G9" s="41" t="s">
         <v>1</v>
@@ -3076,7 +3039,7 @@
       </c>
       <c r="L9" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M9" s="42" t="str">
         <f t="shared" si="5"/>
@@ -3088,15 +3051,15 @@
       </c>
       <c r="O9" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Box</v>
+        <v>SUS.Posto</v>
       </c>
       <c r="P9" s="42" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="Q9" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="R9" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="R9" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S9" s="42" t="str">
@@ -3109,47 +3072,47 @@
       </c>
       <c r="U9" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Box</v>
+        <v>SUS.Posto</v>
       </c>
       <c r="V9" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W9" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W9" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-9</v>
       </c>
       <c r="X9" s="43" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="Y9" s="43" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="Z9" s="44" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AA9" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to a closed and small environment, usually to serve patients.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>It refers to a nursing station associated with an infirmary.</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="40">
         <v>10</v>
       </c>
-      <c r="B10" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>108</v>
+      <c r="B10" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="60" t="s">
+        <v>119</v>
       </c>
       <c r="G10" s="41" t="s">
         <v>1</v>
@@ -3168,7 +3131,7 @@
       </c>
       <c r="L10" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M10" s="42" t="str">
         <f t="shared" si="5"/>
@@ -3180,15 +3143,15 @@
       </c>
       <c r="O10" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Consultório</v>
+        <v>SUS.Quarto</v>
       </c>
       <c r="P10" s="42" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="Q10" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="R10" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="R10" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S10" s="42" t="str">
@@ -3201,47 +3164,47 @@
       </c>
       <c r="U10" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Consultório</v>
+        <v>SUS.Quarto</v>
       </c>
       <c r="V10" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W10" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W10" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-10</v>
       </c>
       <c r="X10" s="43" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="Y10" s="43" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="Z10" s="44" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AA10" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to a doctor's office-type environment.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>It refers to a hospitalization room.</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="40">
         <v>11</v>
       </c>
-      <c r="B11" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>111</v>
+      <c r="B11" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>122</v>
       </c>
       <c r="G11" s="41" t="s">
         <v>1</v>
@@ -3260,7 +3223,7 @@
       </c>
       <c r="L11" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M11" s="42" t="str">
         <f t="shared" si="5"/>
@@ -3272,15 +3235,15 @@
       </c>
       <c r="O11" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Enfermaria</v>
+        <v>SUS.Sala</v>
       </c>
       <c r="P11" s="42" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="Q11" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="R11" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="R11" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S11" s="42" t="str">
@@ -3293,47 +3256,47 @@
       </c>
       <c r="U11" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Enfermaria</v>
+        <v>SUS.Sala</v>
       </c>
       <c r="V11" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W11" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W11" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-11</v>
       </c>
       <c r="X11" s="43" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="Y11" s="43" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="Z11" s="44" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AA11" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to an environment equipped to fulfill ward functions.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>It refers to a room to function as administrative or technical service.</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="40">
         <v>12</v>
       </c>
-      <c r="B12" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>113</v>
+      <c r="B12" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>89</v>
       </c>
       <c r="G12" s="41" t="s">
         <v>1</v>
@@ -3352,7 +3315,7 @@
       </c>
       <c r="L12" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M12" s="42" t="str">
         <f t="shared" si="5"/>
@@ -3360,19 +3323,19 @@
       </c>
       <c r="N12" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Funcional</v>
       </c>
       <c r="O12" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Laboratório</v>
+        <v>SUS.Zoneamento</v>
       </c>
       <c r="P12" s="42" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="Q12" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="R12" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="R12" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S12" s="42" t="str">
@@ -3381,51 +3344,51 @@
       </c>
       <c r="T12" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Funcional</v>
       </c>
       <c r="U12" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Laboratório</v>
+        <v>SUS.Zoneamento</v>
       </c>
       <c r="V12" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W12" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W12" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-12</v>
       </c>
       <c r="X12" s="43" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="Z12" s="44" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AA12" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to an environment equipped to perform laboratory functions.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>It refers to a defined zoning.</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="40">
         <v>13</v>
       </c>
-      <c r="B13" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>116</v>
+      <c r="B13" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="G13" s="41" t="s">
         <v>1</v>
@@ -3444,7 +3407,7 @@
       </c>
       <c r="L13" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M13" s="42" t="str">
         <f t="shared" si="5"/>
@@ -3452,19 +3415,19 @@
       </c>
       <c r="N13" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Funcional</v>
       </c>
       <c r="O13" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Piscina</v>
+        <v>SUS.Unidade.Funcional</v>
       </c>
       <c r="P13" s="42" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="Q13" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="R13" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="R13" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S13" s="42" t="str">
@@ -3473,51 +3436,51 @@
       </c>
       <c r="T13" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Funcional</v>
       </c>
       <c r="U13" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Piscina</v>
+        <v>SUS.Unidade.Funcional</v>
       </c>
       <c r="V13" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W13" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W13" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-13</v>
       </c>
       <c r="X13" s="43" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="Y13" s="43" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="Z13" s="44" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AA13" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to a closed or open environment for medical treatment pools.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>They are the functional units of the Unified Health System of Brazil.</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="40">
         <v>14</v>
       </c>
-      <c r="B14" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="51" t="s">
-        <v>119</v>
+      <c r="B14" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>88</v>
       </c>
       <c r="G14" s="41" t="s">
         <v>1</v>
@@ -3536,7 +3499,7 @@
       </c>
       <c r="L14" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M14" s="42" t="str">
         <f t="shared" si="5"/>
@@ -3544,19 +3507,19 @@
       </c>
       <c r="N14" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Funcional</v>
       </c>
       <c r="O14" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Posto</v>
+        <v>SUS.Setor</v>
       </c>
       <c r="P14" s="42" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q14" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="R14" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="R14" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S14" s="42" t="str">
@@ -3565,51 +3528,51 @@
       </c>
       <c r="T14" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Funcional</v>
       </c>
       <c r="U14" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Posto</v>
+        <v>SUS.Setor</v>
       </c>
       <c r="V14" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W14" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W14" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-14</v>
       </c>
       <c r="X14" s="43" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="Y14" s="43" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="Z14" s="44" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AA14" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to a nursing station associated with an infirmary.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>They are the Sectors of the Unified Health System of Brazil.</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="40">
         <v>15</v>
       </c>
-      <c r="B15" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="50" t="s">
+      <c r="B15" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F15" s="51" t="s">
-        <v>120</v>
+      <c r="E15" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>151</v>
       </c>
       <c r="G15" s="41" t="s">
         <v>1</v>
@@ -3628,80 +3591,80 @@
       </c>
       <c r="L15" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M15" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="N15" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="O15" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Quarto</v>
+        <v>SUS.Robot</v>
       </c>
       <c r="P15" s="42" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="Q15" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="R15" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="R15" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S15" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="T15" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="U15" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Quarto</v>
+        <v>SUS.Robot</v>
       </c>
       <c r="V15" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W15" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W15" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-15</v>
       </c>
       <c r="X15" s="43" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="Y15" s="43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AA15" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to a hospitalization room.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="40">
         <v>16</v>
       </c>
-      <c r="B16" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" s="50" t="s">
+      <c r="B16" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="E16" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F16" s="52" t="s">
-        <v>123</v>
+      <c r="E16" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="62" t="s">
+        <v>90</v>
       </c>
       <c r="G16" s="41" t="s">
         <v>1</v>
@@ -3720,80 +3683,80 @@
       </c>
       <c r="L16" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M16" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="N16" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="O16" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Sala</v>
+        <v>SUS.Equipamento</v>
       </c>
       <c r="P16" s="42" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="Q16" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="R16" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="R16" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="T16" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="U16" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Sala</v>
+        <v>SUS.Equipamento</v>
       </c>
       <c r="V16" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W16" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W16" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-16</v>
       </c>
       <c r="X16" s="43" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="Y16" s="43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Z16" s="44" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AA16" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to a room to function as administrative or technical service.</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="40">
         <v>17</v>
       </c>
-      <c r="B17" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="50" t="s">
+      <c r="B17" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="E17" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="F17" s="53" t="s">
-        <v>89</v>
+      <c r="E17" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>91</v>
       </c>
       <c r="G17" s="41" t="s">
         <v>1</v>
@@ -3812,80 +3775,80 @@
       </c>
       <c r="L17" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M17" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="N17" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Funcional</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="O17" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Zoneamento</v>
+        <v>SUS.Dispositivo</v>
       </c>
       <c r="P17" s="42" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="Q17" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="R17" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="R17" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S17" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="T17" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Funcional</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="U17" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Zoneamento</v>
+        <v>SUS.Dispositivo</v>
       </c>
       <c r="V17" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W17" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W17" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-17</v>
       </c>
       <c r="X17" s="43" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="Y17" s="43" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="Z17" s="44" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AA17" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>It refers to a defined zoning.</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="40">
         <v>18</v>
       </c>
-      <c r="B18" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="50" t="s">
+      <c r="B18" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="E18" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="F18" s="53" t="s">
-        <v>87</v>
+      <c r="E18" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="62" t="s">
+        <v>143</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>1</v>
@@ -3904,80 +3867,80 @@
       </c>
       <c r="L18" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M18" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="N18" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Funcional</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="O18" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Unidade.Funcional</v>
+        <v>SUS.Instrumento</v>
       </c>
       <c r="P18" s="42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q18" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="R18" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="R18" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S18" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="T18" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Funcional</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="U18" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Unidade.Funcional</v>
+        <v>SUS.Instrumento</v>
       </c>
       <c r="V18" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W18" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W18" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-18</v>
       </c>
       <c r="X18" s="43" t="s">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="Y18" s="43" t="s">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="Z18" s="44" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AA18" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>They are the functional units of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>19</v>
       </c>
-      <c r="B19" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="50" t="s">
+      <c r="B19" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="F19" s="53" t="s">
-        <v>88</v>
+      <c r="E19" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>145</v>
       </c>
       <c r="G19" s="41" t="s">
         <v>1</v>
@@ -3996,80 +3959,80 @@
       </c>
       <c r="L19" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M19" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="N19" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Funcional</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="O19" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Setor</v>
+        <v>SUS.Mobília.de.Saúde</v>
       </c>
       <c r="P19" s="42" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="Q19" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="R19" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="R19" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S19" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
+        <v>SUS.Assistência.Médica</v>
       </c>
       <c r="T19" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Funcional</v>
+        <v>SUS.Equipamentos</v>
       </c>
       <c r="U19" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Setor</v>
+        <v>SUS.Mobília.de.Saúde</v>
       </c>
       <c r="V19" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W19" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W19" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-19</v>
       </c>
       <c r="X19" s="43" t="s">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="Y19" s="43" t="s">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="Z19" s="44" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AA19" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>They are the Sectors of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>20</v>
       </c>
-      <c r="B20" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F20" s="53" t="s">
-        <v>155</v>
+      <c r="B20" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="62" t="s">
+        <v>92</v>
       </c>
       <c r="G20" s="41" t="s">
         <v>1</v>
@@ -4088,7 +4051,7 @@
       </c>
       <c r="L20" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M20" s="42" t="str">
         <f t="shared" si="5"/>
@@ -4096,19 +4059,19 @@
       </c>
       <c r="N20" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Equipamentos</v>
+        <v>SUS.Hotelaria</v>
       </c>
       <c r="O20" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Robot</v>
+        <v>SUS.Mobília</v>
       </c>
       <c r="P20" s="42" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="Q20" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="R20" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="R20" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S20" s="42" t="str">
@@ -4117,51 +4080,51 @@
       </c>
       <c r="T20" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
+        <v>SUS.Hotelaria</v>
       </c>
       <c r="U20" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Robot</v>
+        <v>SUS.Mobília</v>
       </c>
       <c r="V20" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W20" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W20" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-20</v>
       </c>
       <c r="X20" s="43" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="Y20" s="43" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Z20" s="44" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AA20" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>21</v>
       </c>
-      <c r="B21" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F21" s="53" t="s">
-        <v>90</v>
+      <c r="B21" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>159</v>
       </c>
       <c r="G21" s="41" t="s">
         <v>1</v>
@@ -4180,7 +4143,7 @@
       </c>
       <c r="L21" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS</v>
+        <v>SomaSUS</v>
       </c>
       <c r="M21" s="42" t="str">
         <f t="shared" si="5"/>
@@ -4188,19 +4151,19 @@
       </c>
       <c r="N21" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SUS.Equipamentos</v>
+        <v>SUS.Hotelaria</v>
       </c>
       <c r="O21" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Equipamento</v>
+        <v>SUS.Roupa</v>
       </c>
       <c r="P21" s="42" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="Q21" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="R21" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="R21" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S21" s="42" t="str">
@@ -4209,51 +4172,51 @@
       </c>
       <c r="T21" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
+        <v>SUS.Hotelaria</v>
       </c>
       <c r="U21" s="42" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Equipamento</v>
+        <v>SUS.Roupa</v>
       </c>
       <c r="V21" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W21" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W21" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-21</v>
       </c>
       <c r="X21" s="43" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="Y21" s="43" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Z21" s="44" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AA21" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>22</v>
       </c>
-      <c r="B22" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>91</v>
+      <c r="B22" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="F22" s="62" t="s">
+        <v>148</v>
       </c>
       <c r="G22" s="41" t="s">
         <v>1</v>
@@ -4271,566 +4234,123 @@
         <v>1</v>
       </c>
       <c r="L22" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS</v>
+        <f t="shared" ref="L22:N22" si="10">CONCATENATE("", C22)</f>
+        <v>SomaSUS</v>
       </c>
       <c r="M22" s="42" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>SUS.Assistência.Médica</v>
       </c>
       <c r="N22" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Equipamentos</v>
+        <f t="shared" si="10"/>
+        <v>SUS.Hotelaria</v>
       </c>
       <c r="O22" s="42" t="str">
         <f t="shared" si="6"/>
-        <v>SUS.Dispositivo</v>
+        <v>SUS.Alimentação</v>
       </c>
       <c r="P22" s="42" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="Q22" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="R22" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="R22" s="44" t="s">
         <v>1</v>
       </c>
       <c r="S22" s="42" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="S22:U22" si="11">SUBSTITUTE(D22, "_", " ")</f>
         <v>SUS.Assistência.Médica</v>
       </c>
       <c r="T22" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
+        <f t="shared" si="11"/>
+        <v>SUS.Hotelaria</v>
       </c>
       <c r="U22" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Dispositivo</v>
+        <f t="shared" si="11"/>
+        <v>SUS.Alimentação</v>
       </c>
       <c r="V22" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W22" s="55" t="str">
-        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="W22" s="46" t="str">
+        <f t="shared" si="8"/>
         <v>Key-SUS-22</v>
       </c>
       <c r="X22" s="43" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="Y22" s="43" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Z22" s="44" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AA22" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="40">
-        <v>23</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F23" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L23" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS</v>
-      </c>
-      <c r="M23" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="N23" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="O23" s="42" t="str">
-        <f t="shared" si="6"/>
-        <v>SUS.Instrumento</v>
-      </c>
-      <c r="P23" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q23" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="R23" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S23" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T23" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="U23" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Instrumento</v>
-      </c>
-      <c r="V23" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W23" s="55" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-SUS-23</v>
-      </c>
-      <c r="X23" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y23" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z23" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA23" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="40">
-        <v>24</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F24" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K24" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS</v>
-      </c>
-      <c r="M24" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="N24" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="O24" s="42" t="str">
-        <f t="shared" si="6"/>
-        <v>SUS.Mobília.de.Saúde</v>
-      </c>
-      <c r="P24" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q24" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="R24" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S24" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T24" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="U24" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Mobília.de.Saúde</v>
-      </c>
-      <c r="V24" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W24" s="55" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-SUS-24</v>
-      </c>
-      <c r="X24" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y24" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z24" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA24" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="40">
-        <v>25</v>
-      </c>
-      <c r="B25" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="F25" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L25" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS</v>
-      </c>
-      <c r="M25" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="N25" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="O25" s="42" t="str">
-        <f t="shared" si="6"/>
-        <v>SUS.Mobília</v>
-      </c>
-      <c r="P25" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q25" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="R25" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S25" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T25" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="U25" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Mobília</v>
-      </c>
-      <c r="V25" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W25" s="55" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-SUS-25</v>
-      </c>
-      <c r="X25" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y25" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z25" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA25" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="40">
-        <v>26</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="F26" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="G26" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K26" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L26" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS</v>
-      </c>
-      <c r="M26" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="N26" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="O26" s="42" t="str">
-        <f t="shared" si="6"/>
-        <v>SUS.Roupa</v>
-      </c>
-      <c r="P26" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q26" s="42" t="s">
-        <v>151</v>
-      </c>
-      <c r="R26" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S26" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T26" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="U26" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Roupa</v>
-      </c>
-      <c r="V26" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W26" s="55" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-SUS-26</v>
-      </c>
-      <c r="X26" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y26" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z26" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA26" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="40">
-        <v>27</v>
-      </c>
-      <c r="B27" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="F27" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="G27" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K27" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L27" s="42" t="str">
-        <f t="shared" ref="L27:N27" si="9">CONCATENATE("", C27)</f>
-        <v>SUS</v>
-      </c>
-      <c r="M27" s="42" t="str">
         <f t="shared" si="9"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="N27" s="42" t="str">
-        <f t="shared" si="9"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="O27" s="42" t="str">
-        <f t="shared" si="6"/>
-        <v>SUS.Alimentação</v>
-      </c>
-      <c r="P27" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q27" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="R27" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S27" s="42" t="str">
-        <f t="shared" ref="S27:U27" si="10">SUBSTITUTE(D27, "_", " ")</f>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T27" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="U27" s="42" t="str">
-        <f t="shared" si="10"/>
-        <v>SUS.Alimentação</v>
-      </c>
-      <c r="V27" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="W27" s="55" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-SUS-27</v>
-      </c>
-      <c r="X27" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y27" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z27" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA27" s="43" t="str">
-        <f t="shared" si="8"/>
         <v>Elements for feeding used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B27">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+  <conditionalFormatting sqref="A3:B22">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:F27 L7:Q27">
-    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
+  <conditionalFormatting sqref="D3:F22 L3:Q22">
+    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+  <conditionalFormatting sqref="F3:F18">
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F23">
-    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
+  <conditionalFormatting sqref="F19:F22">
+    <cfRule type="duplicateValues" dxfId="21" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:XFD7 S7:V27 X8:XFD17 Z18:XFD19 X20:XFD27 V2:V6">
-    <cfRule type="cellIs" dxfId="11" priority="19" operator="equal">
+  <conditionalFormatting sqref="X3:XFD22">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+  <conditionalFormatting sqref="S3:V22">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1">
+    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B2">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:F2 L2:Q2">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:XFD2 S2:V2">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:W1 A28:XFD1048576 AB1:XFD1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:W1 A23:XFD1048576 AB1:XFD1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4839,19 +4359,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.3828125" style="5"/>
+    <col min="22" max="16384" width="5.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="30" t="s">
         <v>13</v>
       </c>
@@ -4916,7 +4436,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -4984,7 +4504,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5000,25 +4520,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="16.3046875" customWidth="1"/>
-    <col min="3" max="3" width="19.3828125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9">
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -5031,7 +4551,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5043,26 +4563,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.69140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3828125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.84375" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.69140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.84375" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.53515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -5109,7 +4629,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -5117,37 +4637,37 @@
         <v>78</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="37" t="s">
         <v>83</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="F2" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="J2" s="37" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="N2" s="37" t="s">
         <v>1</v>
@@ -5156,7 +4676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -5164,37 +4684,37 @@
         <v>79</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="37" t="s">
         <v>83</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="F3" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I3" s="32" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="J3" s="37" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="N3" s="37" t="s">
         <v>1</v>
@@ -5203,7 +4723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -5211,37 +4731,37 @@
         <v>80</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" s="37" t="s">
         <v>83</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="F4" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="N4" s="37" t="s">
         <v>1</v>
@@ -5250,7 +4770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -5258,37 +4778,37 @@
         <v>81</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="37" t="s">
         <v>83</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="F5" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="J5" s="37" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="N5" s="37" t="s">
         <v>1</v>
@@ -5299,37 +4819,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
